--- a/research/traditional_assets/database/data/new_zealand/new_zealand_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_food_wholesalers.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nzse_ccc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0164</v>
+        <v>0.0415</v>
       </c>
       <c r="G2">
-        <v>-0.597972972972973</v>
+        <v>0.1481865284974093</v>
       </c>
       <c r="H2">
-        <v>-0.597972972972973</v>
+        <v>0.1481865284974093</v>
       </c>
       <c r="I2">
-        <v>-0.3750000000000001</v>
+        <v>0.05984455958549223</v>
       </c>
       <c r="J2">
-        <v>-0.3750000000000001</v>
+        <v>0.05984455958549223</v>
       </c>
       <c r="K2">
-        <v>-0.875</v>
+        <v>-0.233</v>
       </c>
       <c r="L2">
-        <v>-0.2956081081081081</v>
+        <v>-0.06036269430051814</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.854</v>
+        <v>0.443</v>
       </c>
       <c r="V2">
-        <v>0.05023529411764706</v>
+        <v>0.03233576642335766</v>
       </c>
       <c r="W2">
-        <v>36.45833333333334</v>
+        <v>0.1713235294117647</v>
       </c>
       <c r="X2">
-        <v>0.05858612716113637</v>
+        <v>0.0894775297395686</v>
       </c>
       <c r="Y2">
-        <v>36.3997472061722</v>
+        <v>0.08184599967219611</v>
       </c>
       <c r="Z2">
-        <v>0.223463687150838</v>
+        <v>0.4495690659212672</v>
       </c>
       <c r="AA2">
-        <v>-0.08379888268156427</v>
+        <v>0.02690426275331936</v>
       </c>
       <c r="AB2">
-        <v>0.0365921466101671</v>
+        <v>0.06391751449936263</v>
       </c>
       <c r="AC2">
-        <v>-0.1203910292917314</v>
+        <v>-0.03701325174604327</v>
       </c>
       <c r="AD2">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="AG2">
-        <v>18.046</v>
+        <v>13.957</v>
       </c>
       <c r="AH2">
-        <v>0.5264623955431754</v>
+        <v>0.5124555160142349</v>
       </c>
       <c r="AI2">
-        <v>1.077537058152794</v>
+        <v>0.9119696010132995</v>
       </c>
       <c r="AJ2">
-        <v>0.5149232437368031</v>
+        <v>0.5046462016849261</v>
       </c>
       <c r="AK2">
-        <v>1.081505453673739</v>
+        <v>0.9094285528116244</v>
       </c>
       <c r="AL2">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="AM2">
-        <v>0.697</v>
+        <v>0.391</v>
       </c>
       <c r="AN2">
-        <v>-21.42857142857143</v>
+        <v>32.72727272727273</v>
       </c>
       <c r="AO2">
-        <v>-0.7449664429530202</v>
+        <v>0.2221153846153846</v>
       </c>
       <c r="AP2">
-        <v>-20.46031746031746</v>
+        <v>31.72045454545455</v>
       </c>
       <c r="AQ2">
-        <v>-1.592539454806313</v>
+        <v>0.5907928388746803</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cooks Global Foods Limited (NZSE:CGF)</t>
+          <t>Cooks Coffee Company Limited (NZSE:CCC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0164</v>
+        <v>0.0415</v>
       </c>
       <c r="G3">
-        <v>-0.597972972972973</v>
+        <v>0.1481865284974093</v>
       </c>
       <c r="H3">
-        <v>-0.597972972972973</v>
+        <v>0.1481865284974093</v>
       </c>
       <c r="I3">
-        <v>-0.3750000000000001</v>
+        <v>0.05984455958549223</v>
       </c>
       <c r="J3">
-        <v>-0.3750000000000001</v>
+        <v>0.05984455958549223</v>
       </c>
       <c r="K3">
-        <v>-0.875</v>
+        <v>-0.233</v>
       </c>
       <c r="L3">
-        <v>-0.2956081081081081</v>
+        <v>-0.06036269430051814</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.854</v>
+        <v>0.443</v>
       </c>
       <c r="V3">
-        <v>0.05023529411764706</v>
+        <v>0.03233576642335766</v>
       </c>
       <c r="W3">
-        <v>36.45833333333334</v>
+        <v>0.1713235294117647</v>
       </c>
       <c r="X3">
-        <v>0.05858612716113637</v>
+        <v>0.0894775297395686</v>
       </c>
       <c r="Y3">
-        <v>36.3997472061722</v>
+        <v>0.08184599967219611</v>
       </c>
       <c r="Z3">
-        <v>0.223463687150838</v>
+        <v>0.4495690659212672</v>
       </c>
       <c r="AA3">
-        <v>-0.08379888268156427</v>
+        <v>0.02690426275331936</v>
       </c>
       <c r="AB3">
-        <v>0.0365921466101671</v>
+        <v>0.06391751449936263</v>
       </c>
       <c r="AC3">
-        <v>-0.1203910292917314</v>
+        <v>-0.03701325174604327</v>
       </c>
       <c r="AD3">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="AG3">
-        <v>18.046</v>
+        <v>13.957</v>
       </c>
       <c r="AH3">
-        <v>0.5264623955431754</v>
+        <v>0.5124555160142349</v>
       </c>
       <c r="AI3">
-        <v>1.077537058152794</v>
+        <v>0.9119696010132995</v>
       </c>
       <c r="AJ3">
-        <v>0.5149232437368031</v>
+        <v>0.5046462016849261</v>
       </c>
       <c r="AK3">
-        <v>1.081505453673739</v>
+        <v>0.9094285528116244</v>
       </c>
       <c r="AL3">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="AM3">
-        <v>0.697</v>
+        <v>0.391</v>
       </c>
       <c r="AN3">
-        <v>-21.42857142857143</v>
+        <v>32.72727272727273</v>
       </c>
       <c r="AO3">
-        <v>-0.7449664429530202</v>
+        <v>0.2221153846153846</v>
       </c>
       <c r="AP3">
-        <v>-20.46031746031746</v>
+        <v>31.72045454545455</v>
       </c>
       <c r="AQ3">
-        <v>-1.592539454806313</v>
+        <v>0.5907928388746803</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cooks Coffee Company Limited (NZSE:CCC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NZSE:CCC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Food Wholesalers</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.512455516014235</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>13.7</v>
+      </c>
+      <c r="H2">
+        <v>24.3166136256866</v>
+      </c>
+      <c r="I2">
+        <v>27.657</v>
+      </c>
+      <c r="J2">
+        <v>24.1546136256866</v>
+      </c>
+      <c r="K2">
+        <v>14.4</v>
+      </c>
+      <c r="L2">
+        <v>0.281</v>
+      </c>
+      <c r="M2">
+        <v>0.0639175144993626</v>
+      </c>
+      <c r="N2">
+        <v>0.06755952020073459</v>
+      </c>
+      <c r="O2">
+        <v>0.0396</v>
+      </c>
+      <c r="P2">
+        <v>0.03816</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.0894775297395686</v>
+      </c>
+      <c r="T2">
+        <v>0.0678564850512471</v>
+      </c>
+      <c r="U2">
+        <v>0.856873022997613</v>
+      </c>
+      <c r="V2">
+        <v>0.491296997140472</v>
+      </c>
+      <c r="W2">
+        <v>7.117437722419926</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>13.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.055</v>
+      </c>
+      <c r="AD2">
+        <v>0.28</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.44</v>
+      </c>
+      <c r="AH2">
+        <v>0.334</v>
+      </c>
+      <c r="AI2">
+        <v>0.07100000000000017</v>
+      </c>
+      <c r="AJ2">
+        <v>14.4</v>
+      </c>
+      <c r="AK2">
+        <v>14.4</v>
+      </c>
+      <c r="AL2">
+        <v>1.04</v>
+      </c>
+      <c r="AM2">
+        <v>14.4</v>
+      </c>
+      <c r="AN2">
+        <v>0.443</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.06764669093535357</v>
+      </c>
+      <c r="C2">
+        <v>24.5246217037047</v>
+      </c>
+      <c r="D2">
+        <v>24.0816217037047</v>
+      </c>
+      <c r="E2">
+        <v>-14.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.443</v>
+      </c>
+      <c r="H2">
+        <v>13.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.44</v>
+      </c>
+      <c r="K2">
+        <v>0.334</v>
+      </c>
+      <c r="L2">
+        <v>0.106</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.106</v>
+      </c>
+      <c r="O2">
+        <v>0.02968</v>
+      </c>
+      <c r="P2">
+        <v>0.07631999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>0.41032</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.06764669093535357</v>
+      </c>
+      <c r="T2">
+        <v>0.4877497264029954</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.28</v>
+      </c>
+      <c r="W2">
+        <v>0.032904</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.06755952020073458</v>
+      </c>
+      <c r="C3">
+        <v>24.31661362568659</v>
+      </c>
+      <c r="D3">
+        <v>24.15461362568659</v>
+      </c>
+      <c r="E3">
+        <v>-14.119</v>
+      </c>
+      <c r="F3">
+        <v>0.281</v>
+      </c>
+      <c r="G3">
+        <v>0.443</v>
+      </c>
+      <c r="H3">
+        <v>13.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.44</v>
+      </c>
+      <c r="K3">
+        <v>0.334</v>
+      </c>
+      <c r="L3">
+        <v>0.106</v>
+      </c>
+      <c r="M3">
+        <v>0.014893</v>
+      </c>
+      <c r="N3">
+        <v>0.09110699999999998</v>
+      </c>
+      <c r="O3">
+        <v>0.02550996</v>
+      </c>
+      <c r="P3">
+        <v>0.06559703999999998</v>
+      </c>
+      <c r="Q3">
+        <v>0.39959704</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.06785648505124706</v>
+      </c>
+      <c r="T3">
+        <v>0.4912969971404718</v>
+      </c>
+      <c r="U3">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V3">
+        <v>0.28</v>
+      </c>
+      <c r="W3">
+        <v>0.03816</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>7.117437722419926</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.0680253094661156</v>
+      </c>
+      <c r="C4">
+        <v>23.65064046571662</v>
+      </c>
+      <c r="D4">
+        <v>23.76964046571662</v>
+      </c>
+      <c r="E4">
+        <v>-13.838</v>
+      </c>
+      <c r="F4">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.443</v>
+      </c>
+      <c r="H4">
+        <v>13.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.44</v>
+      </c>
+      <c r="K4">
+        <v>0.334</v>
+      </c>
+      <c r="L4">
+        <v>0.106</v>
+      </c>
+      <c r="M4">
+        <v>0.05136680000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.05463319999999997</v>
+      </c>
+      <c r="O4">
+        <v>0.01529729599999999</v>
+      </c>
+      <c r="P4">
+        <v>0.03933590399999998</v>
+      </c>
+      <c r="Q4">
+        <v>0.373335904</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.06807056067970979</v>
+      </c>
+      <c r="T4">
+        <v>0.4949166611583047</v>
+      </c>
+      <c r="U4">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V4">
+        <v>0.28</v>
+      </c>
+      <c r="W4">
+        <v>0.06580800000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>2.063589711642539</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07169795300104817</v>
+      </c>
+      <c r="C5">
+        <v>20.71605845162278</v>
+      </c>
+      <c r="D5">
+        <v>21.11605845162278</v>
+      </c>
+      <c r="E5">
+        <v>-13.557</v>
+      </c>
+      <c r="F5">
+        <v>0.843</v>
+      </c>
+      <c r="G5">
+        <v>0.443</v>
+      </c>
+      <c r="H5">
+        <v>13.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.44</v>
+      </c>
+      <c r="K5">
+        <v>0.334</v>
+      </c>
+      <c r="L5">
+        <v>0.106</v>
+      </c>
+      <c r="M5">
+        <v>0.1802334</v>
+      </c>
+      <c r="N5">
+        <v>-0.0742334</v>
+      </c>
+      <c r="O5">
+        <v>-0.020785352</v>
+      </c>
+      <c r="P5">
+        <v>-0.053448048</v>
+      </c>
+      <c r="Q5">
+        <v>0.280551952</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.06839193892686113</v>
+      </c>
+      <c r="T5">
+        <v>0.5003506345894766</v>
+      </c>
+      <c r="U5">
+        <v>0.2138</v>
+      </c>
+      <c r="V5">
+        <v>0.1646753598389644</v>
+      </c>
+      <c r="W5">
+        <v>0.1785924080664294</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.5881262851391584</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07446287240811457</v>
+      </c>
+      <c r="C6">
+        <v>18.79794411193892</v>
+      </c>
+      <c r="D6">
+        <v>19.47894411193892</v>
+      </c>
+      <c r="E6">
+        <v>-13.276</v>
+      </c>
+      <c r="F6">
+        <v>1.124</v>
+      </c>
+      <c r="G6">
+        <v>0.443</v>
+      </c>
+      <c r="H6">
+        <v>13.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.44</v>
+      </c>
+      <c r="K6">
+        <v>0.334</v>
+      </c>
+      <c r="L6">
+        <v>0.106</v>
+      </c>
+      <c r="M6">
+        <v>0.2684112</v>
+      </c>
+      <c r="N6">
+        <v>-0.1624112</v>
+      </c>
+      <c r="O6">
+        <v>-0.04547513600000001</v>
+      </c>
+      <c r="P6">
+        <v>-0.116936064</v>
+      </c>
+      <c r="Q6">
+        <v>0.217063936</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0687157293397101</v>
+      </c>
+      <c r="T6">
+        <v>0.5058253937441028</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>0.1105766078315659</v>
+      </c>
+      <c r="W6">
+        <v>0.2123943060498221</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.3949164565413067</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07646287240811457</v>
+      </c>
+      <c r="C7">
+        <v>17.48255969744895</v>
+      </c>
+      <c r="D7">
+        <v>18.44455969744895</v>
+      </c>
+      <c r="E7">
+        <v>-12.995</v>
+      </c>
+      <c r="F7">
+        <v>1.405</v>
+      </c>
+      <c r="G7">
+        <v>0.443</v>
+      </c>
+      <c r="H7">
+        <v>13.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.44</v>
+      </c>
+      <c r="K7">
+        <v>0.334</v>
+      </c>
+      <c r="L7">
+        <v>0.106</v>
+      </c>
+      <c r="M7">
+        <v>0.3355140000000001</v>
+      </c>
+      <c r="N7">
+        <v>-0.2295140000000001</v>
+      </c>
+      <c r="O7">
+        <v>-0.06426392000000003</v>
+      </c>
+      <c r="P7">
+        <v>-0.1652500800000001</v>
+      </c>
+      <c r="Q7">
+        <v>0.1687499199999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.0690306317538123</v>
+      </c>
+      <c r="T7">
+        <v>0.5111498715729881</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>0.08846128626525268</v>
+      </c>
+      <c r="W7">
+        <v>0.2176754448398577</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.3159331652330453</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07846287240811457</v>
+      </c>
+      <c r="C8">
+        <v>16.2714929333648</v>
+      </c>
+      <c r="D8">
+        <v>17.5144929333648</v>
+      </c>
+      <c r="E8">
+        <v>-12.714</v>
+      </c>
+      <c r="F8">
+        <v>1.686</v>
+      </c>
+      <c r="G8">
+        <v>0.443</v>
+      </c>
+      <c r="H8">
+        <v>13.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.44</v>
+      </c>
+      <c r="K8">
+        <v>0.334</v>
+      </c>
+      <c r="L8">
+        <v>0.106</v>
+      </c>
+      <c r="M8">
+        <v>0.4026168</v>
+      </c>
+      <c r="N8">
+        <v>-0.2966168</v>
+      </c>
+      <c r="O8">
+        <v>-0.083052704</v>
+      </c>
+      <c r="P8">
+        <v>-0.213564096</v>
+      </c>
+      <c r="Q8">
+        <v>0.120435904</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0693522342192784</v>
+      </c>
+      <c r="T8">
+        <v>0.5165876361641901</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>0.07371773855437726</v>
+      </c>
+      <c r="W8">
+        <v>0.2211962040332147</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.2632776376942044</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08046287240811457</v>
+      </c>
+      <c r="C9">
+        <v>15.14972070999051</v>
+      </c>
+      <c r="D9">
+        <v>16.67372070999051</v>
+      </c>
+      <c r="E9">
+        <v>-12.433</v>
+      </c>
+      <c r="F9">
+        <v>1.967</v>
+      </c>
+      <c r="G9">
+        <v>0.443</v>
+      </c>
+      <c r="H9">
+        <v>13.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.44</v>
+      </c>
+      <c r="K9">
+        <v>0.334</v>
+      </c>
+      <c r="L9">
+        <v>0.106</v>
+      </c>
+      <c r="M9">
+        <v>0.4697196000000001</v>
+      </c>
+      <c r="N9">
+        <v>-0.3637196000000001</v>
+      </c>
+      <c r="O9">
+        <v>-0.101841488</v>
+      </c>
+      <c r="P9">
+        <v>-0.2618781120000001</v>
+      </c>
+      <c r="Q9">
+        <v>0.07212188799999997</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.06968075286679752</v>
+      </c>
+      <c r="T9">
+        <v>0.5221423419293965</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>0.06318663304660907</v>
+      </c>
+      <c r="W9">
+        <v>0.2237110320284698</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.2256665465950324</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08246287240811458</v>
+      </c>
+      <c r="C10">
+        <v>14.10497248224488</v>
+      </c>
+      <c r="D10">
+        <v>15.90997248224488</v>
+      </c>
+      <c r="E10">
+        <v>-12.152</v>
+      </c>
+      <c r="F10">
+        <v>2.248</v>
+      </c>
+      <c r="G10">
+        <v>0.443</v>
+      </c>
+      <c r="H10">
+        <v>13.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.44</v>
+      </c>
+      <c r="K10">
+        <v>0.334</v>
+      </c>
+      <c r="L10">
+        <v>0.106</v>
+      </c>
+      <c r="M10">
+        <v>0.5368224</v>
+      </c>
+      <c r="N10">
+        <v>-0.4308224</v>
+      </c>
+      <c r="O10">
+        <v>-0.120630272</v>
+      </c>
+      <c r="P10">
+        <v>-0.310192128</v>
+      </c>
+      <c r="Q10">
+        <v>0.02380787200000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.07001641322404531</v>
+      </c>
+      <c r="T10">
+        <v>0.5278178021677594</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>0.05528830391578294</v>
+      </c>
+      <c r="W10">
+        <v>0.225597153024911</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.1974582282706533</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08446287240811459</v>
+      </c>
+      <c r="C11">
+        <v>13.12712746820158</v>
+      </c>
+      <c r="D11">
+        <v>15.21312746820158</v>
+      </c>
+      <c r="E11">
+        <v>-11.871</v>
+      </c>
+      <c r="F11">
+        <v>2.529</v>
+      </c>
+      <c r="G11">
+        <v>0.443</v>
+      </c>
+      <c r="H11">
+        <v>13.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.44</v>
+      </c>
+      <c r="K11">
+        <v>0.334</v>
+      </c>
+      <c r="L11">
+        <v>0.106</v>
+      </c>
+      <c r="M11">
+        <v>0.6039252000000001</v>
+      </c>
+      <c r="N11">
+        <v>-0.4979252000000001</v>
+      </c>
+      <c r="O11">
+        <v>-0.139419056</v>
+      </c>
+      <c r="P11">
+        <v>-0.358506144</v>
+      </c>
+      <c r="Q11">
+        <v>-0.02450614400000001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.07035945073200187</v>
+      </c>
+      <c r="T11">
+        <v>0.5336179977959766</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.0491451590362515</v>
+      </c>
+      <c r="W11">
+        <v>0.2270641360221431</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.1755184251294696</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08646287240811458</v>
+      </c>
+      <c r="C12">
+        <v>12.20776361392361</v>
+      </c>
+      <c r="D12">
+        <v>14.57476361392361</v>
+      </c>
+      <c r="E12">
+        <v>-11.59</v>
+      </c>
+      <c r="F12">
+        <v>2.81</v>
+      </c>
+      <c r="G12">
+        <v>0.443</v>
+      </c>
+      <c r="H12">
+        <v>13.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.44</v>
+      </c>
+      <c r="K12">
+        <v>0.334</v>
+      </c>
+      <c r="L12">
+        <v>0.106</v>
+      </c>
+      <c r="M12">
+        <v>0.6710280000000002</v>
+      </c>
+      <c r="N12">
+        <v>-0.5650280000000002</v>
+      </c>
+      <c r="O12">
+        <v>-0.1582078400000001</v>
+      </c>
+      <c r="P12">
+        <v>-0.4068201600000001</v>
+      </c>
+      <c r="Q12">
+        <v>-0.07282016000000008</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.07071011129569077</v>
+      </c>
+      <c r="T12">
+        <v>0.5395470866603763</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.04423064313262634</v>
+      </c>
+      <c r="W12">
+        <v>0.2282377224199288</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.1579665826165226</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08846287240811457</v>
+      </c>
+      <c r="C13">
+        <v>11.33981554156274</v>
+      </c>
+      <c r="D13">
+        <v>13.98781554156274</v>
+      </c>
+      <c r="E13">
+        <v>-11.309</v>
+      </c>
+      <c r="F13">
+        <v>3.091</v>
+      </c>
+      <c r="G13">
+        <v>0.443</v>
+      </c>
+      <c r="H13">
+        <v>13.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.44</v>
+      </c>
+      <c r="K13">
+        <v>0.334</v>
+      </c>
+      <c r="L13">
+        <v>0.106</v>
+      </c>
+      <c r="M13">
+        <v>0.7381308000000001</v>
+      </c>
+      <c r="N13">
+        <v>-0.6321308000000001</v>
+      </c>
+      <c r="O13">
+        <v>-0.176996624</v>
+      </c>
+      <c r="P13">
+        <v>-0.4551341760000001</v>
+      </c>
+      <c r="Q13">
+        <v>-0.121134176</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.07106865187204685</v>
+      </c>
+      <c r="T13">
+        <v>0.545609413476785</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.04020967557511487</v>
+      </c>
+      <c r="W13">
+        <v>0.2291979294726626</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.1436059841968388</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09046287240811457</v>
+      </c>
+      <c r="C14">
+        <v>10.51731194760594</v>
+      </c>
+      <c r="D14">
+        <v>13.44631194760594</v>
+      </c>
+      <c r="E14">
+        <v>-11.028</v>
+      </c>
+      <c r="F14">
+        <v>3.372</v>
+      </c>
+      <c r="G14">
+        <v>0.443</v>
+      </c>
+      <c r="H14">
+        <v>13.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.44</v>
+      </c>
+      <c r="K14">
+        <v>0.334</v>
+      </c>
+      <c r="L14">
+        <v>0.106</v>
+      </c>
+      <c r="M14">
+        <v>0.8052336</v>
+      </c>
+      <c r="N14">
+        <v>-0.6992336</v>
+      </c>
+      <c r="O14">
+        <v>-0.195785408</v>
+      </c>
+      <c r="P14">
+        <v>-0.503448192</v>
+      </c>
+      <c r="Q14">
+        <v>-0.169448192</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.07143534109786556</v>
+      </c>
+      <c r="T14">
+        <v>0.5518095204481123</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.03685886927718863</v>
+      </c>
+      <c r="W14">
+        <v>0.2299981020166074</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.1316388188471023</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09246287240811457</v>
+      </c>
+      <c r="C15">
+        <v>9.73517172367813</v>
+      </c>
+      <c r="D15">
+        <v>12.94517172367813</v>
+      </c>
+      <c r="E15">
+        <v>-10.747</v>
+      </c>
+      <c r="F15">
+        <v>3.653</v>
+      </c>
+      <c r="G15">
+        <v>0.443</v>
+      </c>
+      <c r="H15">
+        <v>13.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.44</v>
+      </c>
+      <c r="K15">
+        <v>0.334</v>
+      </c>
+      <c r="L15">
+        <v>0.106</v>
+      </c>
+      <c r="M15">
+        <v>0.8723364000000001</v>
+      </c>
+      <c r="N15">
+        <v>-0.7663364000000001</v>
+      </c>
+      <c r="O15">
+        <v>-0.2145741920000001</v>
+      </c>
+      <c r="P15">
+        <v>-0.5517622080000001</v>
+      </c>
+      <c r="Q15">
+        <v>-0.2177622080000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.07181045996105942</v>
+      </c>
+      <c r="T15">
+        <v>0.5581521586141824</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.03402357164048181</v>
+      </c>
+      <c r="W15">
+        <v>0.230675171092253</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.1215127558588636</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09446287240811457</v>
+      </c>
+      <c r="C16">
+        <v>8.989044030347273</v>
+      </c>
+      <c r="D16">
+        <v>12.48004403034727</v>
+      </c>
+      <c r="E16">
+        <v>-10.466</v>
+      </c>
+      <c r="F16">
+        <v>3.934000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.443</v>
+      </c>
+      <c r="H16">
+        <v>13.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.44</v>
+      </c>
+      <c r="K16">
+        <v>0.334</v>
+      </c>
+      <c r="L16">
+        <v>0.106</v>
+      </c>
+      <c r="M16">
+        <v>0.9394392000000001</v>
+      </c>
+      <c r="N16">
+        <v>-0.8334392000000002</v>
+      </c>
+      <c r="O16">
+        <v>-0.2333629760000001</v>
+      </c>
+      <c r="P16">
+        <v>-0.6000762240000002</v>
+      </c>
+      <c r="Q16">
+        <v>-0.2660762240000001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.07219430251874615</v>
+      </c>
+      <c r="T16">
+        <v>0.5646422999934171</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.03159331652330453</v>
+      </c>
+      <c r="W16">
+        <v>0.2312555160142349</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.1128332732975161</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09646287240811457</v>
+      </c>
+      <c r="C17">
+        <v>8.275181652558716</v>
+      </c>
+      <c r="D17">
+        <v>12.04718165255872</v>
+      </c>
+      <c r="E17">
+        <v>-10.185</v>
+      </c>
+      <c r="F17">
+        <v>4.215</v>
+      </c>
+      <c r="G17">
+        <v>0.443</v>
+      </c>
+      <c r="H17">
+        <v>13.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.44</v>
+      </c>
+      <c r="K17">
+        <v>0.334</v>
+      </c>
+      <c r="L17">
+        <v>0.106</v>
+      </c>
+      <c r="M17">
+        <v>1.006542</v>
+      </c>
+      <c r="N17">
+        <v>-0.9005420000000001</v>
+      </c>
+      <c r="O17">
+        <v>-0.2521517600000001</v>
+      </c>
+      <c r="P17">
+        <v>-0.64839024</v>
+      </c>
+      <c r="Q17">
+        <v>-0.31439024</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.07258717666602552</v>
+      </c>
+      <c r="T17">
+        <v>0.5712851505815749</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.0294870954217509</v>
+      </c>
+      <c r="W17">
+        <v>0.2317584816132859</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.1053110550776818</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09846287240811458</v>
+      </c>
+      <c r="C18">
+        <v>7.590339827104794</v>
+      </c>
+      <c r="D18">
+        <v>11.64333982710479</v>
+      </c>
+      <c r="E18">
+        <v>-9.904</v>
+      </c>
+      <c r="F18">
+        <v>4.496</v>
+      </c>
+      <c r="G18">
+        <v>0.443</v>
+      </c>
+      <c r="H18">
+        <v>13.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.44</v>
+      </c>
+      <c r="K18">
+        <v>0.334</v>
+      </c>
+      <c r="L18">
+        <v>0.106</v>
+      </c>
+      <c r="M18">
+        <v>1.0736448</v>
+      </c>
+      <c r="N18">
+        <v>-0.9676448000000001</v>
+      </c>
+      <c r="O18">
+        <v>-0.2709405440000001</v>
+      </c>
+      <c r="P18">
+        <v>-0.6967042560000001</v>
+      </c>
+      <c r="Q18">
+        <v>-0.3627042560000001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.07298940495966869</v>
+      </c>
+      <c r="T18">
+        <v>0.5780861642789746</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.02764415195789147</v>
+      </c>
+      <c r="W18">
+        <v>0.2321985765124555</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.0987291141353267</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1004628724081146</v>
+      </c>
+      <c r="C19">
+        <v>6.931694758933347</v>
+      </c>
+      <c r="D19">
+        <v>11.26569475893335</v>
+      </c>
+      <c r="E19">
+        <v>-9.622999999999999</v>
+      </c>
+      <c r="F19">
+        <v>4.777000000000001</v>
+      </c>
+      <c r="G19">
+        <v>0.443</v>
+      </c>
+      <c r="H19">
+        <v>13.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.44</v>
+      </c>
+      <c r="K19">
+        <v>0.334</v>
+      </c>
+      <c r="L19">
+        <v>0.106</v>
+      </c>
+      <c r="M19">
+        <v>1.1407476</v>
+      </c>
+      <c r="N19">
+        <v>-1.0347476</v>
+      </c>
+      <c r="O19">
+        <v>-0.2897293280000001</v>
+      </c>
+      <c r="P19">
+        <v>-0.7450182720000001</v>
+      </c>
+      <c r="Q19">
+        <v>-0.4110182720000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.07340132550135145</v>
+      </c>
+      <c r="T19">
+        <v>0.5850510578245045</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.02601802537213314</v>
+      </c>
+      <c r="W19">
+        <v>0.2325868955411346</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.09292151918618985</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1024628724081146</v>
+      </c>
+      <c r="C20">
+        <v>6.296777496554297</v>
+      </c>
+      <c r="D20">
+        <v>10.9117774965543</v>
+      </c>
+      <c r="E20">
+        <v>-9.342000000000001</v>
+      </c>
+      <c r="F20">
+        <v>5.058</v>
+      </c>
+      <c r="G20">
+        <v>0.443</v>
+      </c>
+      <c r="H20">
+        <v>13.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.44</v>
+      </c>
+      <c r="K20">
+        <v>0.334</v>
+      </c>
+      <c r="L20">
+        <v>0.106</v>
+      </c>
+      <c r="M20">
+        <v>1.2078504</v>
+      </c>
+      <c r="N20">
+        <v>-1.1018504</v>
+      </c>
+      <c r="O20">
+        <v>-0.308518112</v>
+      </c>
+      <c r="P20">
+        <v>-0.793332288</v>
+      </c>
+      <c r="Q20">
+        <v>-0.459332288</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.07382329288551426</v>
+      </c>
+      <c r="T20">
+        <v>0.5921858268223643</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.02457257951812575</v>
+      </c>
+      <c r="W20">
+        <v>0.2329320680110716</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.08775921256473496</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1044628724081146</v>
+      </c>
+      <c r="C21">
+        <v>5.683419891826487</v>
+      </c>
+      <c r="D21">
+        <v>10.57941989182649</v>
+      </c>
+      <c r="E21">
+        <v>-9.061</v>
+      </c>
+      <c r="F21">
+        <v>5.339</v>
+      </c>
+      <c r="G21">
+        <v>0.443</v>
+      </c>
+      <c r="H21">
+        <v>13.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.44</v>
+      </c>
+      <c r="K21">
+        <v>0.334</v>
+      </c>
+      <c r="L21">
+        <v>0.106</v>
+      </c>
+      <c r="M21">
+        <v>1.2749532</v>
+      </c>
+      <c r="N21">
+        <v>-1.1689532</v>
+      </c>
+      <c r="O21">
+        <v>-0.3273068960000001</v>
+      </c>
+      <c r="P21">
+        <v>-0.8416463040000002</v>
+      </c>
+      <c r="Q21">
+        <v>-0.5076463040000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.0742556792174342</v>
+      </c>
+      <c r="T21">
+        <v>0.5994967629559738</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.02327928585927703</v>
+      </c>
+      <c r="W21">
+        <v>0.2332409065368047</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.08314030664027505</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1064628724081146</v>
+      </c>
+      <c r="C22">
+        <v>5.089710143768032</v>
+      </c>
+      <c r="D22">
+        <v>10.26671014376803</v>
+      </c>
+      <c r="E22">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="F22">
+        <v>5.620000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.443</v>
+      </c>
+      <c r="H22">
+        <v>13.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.44</v>
+      </c>
+      <c r="K22">
+        <v>0.334</v>
+      </c>
+      <c r="L22">
+        <v>0.106</v>
+      </c>
+      <c r="M22">
+        <v>1.342056</v>
+      </c>
+      <c r="N22">
+        <v>-1.236056</v>
+      </c>
+      <c r="O22">
+        <v>-0.3460956800000002</v>
+      </c>
+      <c r="P22">
+        <v>-0.8899603200000004</v>
+      </c>
+      <c r="Q22">
+        <v>-0.5559603200000003</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.07469887520765212</v>
+      </c>
+      <c r="T22">
+        <v>0.6069904724929234</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.02211532156631317</v>
+      </c>
+      <c r="W22">
+        <v>0.2335188612099644</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.07898329130826121</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1084628724081146</v>
+      </c>
+      <c r="C23">
+        <v>4.513956000309198</v>
+      </c>
+      <c r="D23">
+        <v>9.971956000309198</v>
+      </c>
+      <c r="E23">
+        <v>-8.499000000000001</v>
+      </c>
+      <c r="F23">
+        <v>5.901</v>
+      </c>
+      <c r="G23">
+        <v>0.443</v>
+      </c>
+      <c r="H23">
+        <v>13.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.44</v>
+      </c>
+      <c r="K23">
+        <v>0.334</v>
+      </c>
+      <c r="L23">
+        <v>0.106</v>
+      </c>
+      <c r="M23">
+        <v>1.4091588</v>
+      </c>
+      <c r="N23">
+        <v>-1.3031588</v>
+      </c>
+      <c r="O23">
+        <v>-0.364884464</v>
+      </c>
+      <c r="P23">
+        <v>-0.9382743359999999</v>
+      </c>
+      <c r="Q23">
+        <v>-0.6042743359999998</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.07515329134952112</v>
+      </c>
+      <c r="T23">
+        <v>0.6146738961953654</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.02106221101553636</v>
+      </c>
+      <c r="W23">
+        <v>0.2337703440094899</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.0752221821983442</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1104628724081146</v>
+      </c>
+      <c r="C24">
+        <v>3.954654121938493</v>
+      </c>
+      <c r="D24">
+        <v>9.693654121938494</v>
+      </c>
+      <c r="E24">
+        <v>-8.218</v>
+      </c>
+      <c r="F24">
+        <v>6.182</v>
+      </c>
+      <c r="G24">
+        <v>0.443</v>
+      </c>
+      <c r="H24">
+        <v>13.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.44</v>
+      </c>
+      <c r="K24">
+        <v>0.334</v>
+      </c>
+      <c r="L24">
+        <v>0.106</v>
+      </c>
+      <c r="M24">
+        <v>1.4762616</v>
+      </c>
+      <c r="N24">
+        <v>-1.3702616</v>
+      </c>
+      <c r="O24">
+        <v>-0.3836732480000001</v>
+      </c>
+      <c r="P24">
+        <v>-0.9865883520000001</v>
+      </c>
+      <c r="Q24">
+        <v>-0.652588352</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.07561935918733551</v>
+      </c>
+      <c r="T24">
+        <v>0.6225543307619728</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.02010483778755743</v>
+      </c>
+      <c r="W24">
+        <v>0.2339989647363313</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.07180299209841945</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1124628724081146</v>
+      </c>
+      <c r="C25">
+        <v>3.41046443614311</v>
+      </c>
+      <c r="D25">
+        <v>9.430464436143112</v>
+      </c>
+      <c r="E25">
+        <v>-7.936999999999999</v>
+      </c>
+      <c r="F25">
+        <v>6.463000000000001</v>
+      </c>
+      <c r="G25">
+        <v>0.443</v>
+      </c>
+      <c r="H25">
+        <v>13.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.44</v>
+      </c>
+      <c r="K25">
+        <v>0.334</v>
+      </c>
+      <c r="L25">
+        <v>0.106</v>
+      </c>
+      <c r="M25">
+        <v>1.5433644</v>
+      </c>
+      <c r="N25">
+        <v>-1.4373644</v>
+      </c>
+      <c r="O25">
+        <v>-0.4024620320000001</v>
+      </c>
+      <c r="P25">
+        <v>-1.034902368</v>
+      </c>
+      <c r="Q25">
+        <v>-0.7009023680000002</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.07609753268327493</v>
+      </c>
+      <c r="T25">
+        <v>0.6306394519406996</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.01923071440548971</v>
+      </c>
+      <c r="W25">
+        <v>0.2342077053999691</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.0686811228767491</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1144628724081146</v>
+      </c>
+      <c r="C26">
+        <v>2.880188559190501</v>
+      </c>
+      <c r="D26">
+        <v>9.181188559190501</v>
+      </c>
+      <c r="E26">
+        <v>-7.656000000000001</v>
+      </c>
+      <c r="F26">
+        <v>6.744</v>
+      </c>
+      <c r="G26">
+        <v>0.443</v>
+      </c>
+      <c r="H26">
+        <v>13.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.44</v>
+      </c>
+      <c r="K26">
+        <v>0.334</v>
+      </c>
+      <c r="L26">
+        <v>0.106</v>
+      </c>
+      <c r="M26">
+        <v>1.6104672</v>
+      </c>
+      <c r="N26">
+        <v>-1.5044672</v>
+      </c>
+      <c r="O26">
+        <v>-0.4212508160000001</v>
+      </c>
+      <c r="P26">
+        <v>-1.083216384</v>
+      </c>
+      <c r="Q26">
+        <v>-0.7492163839999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.07658828969226539</v>
+      </c>
+      <c r="T26">
+        <v>0.6389373394662351</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.01842943463859431</v>
+      </c>
+      <c r="W26">
+        <v>0.2343990510083037</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.06581940942355102</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1164628724081146</v>
+      </c>
+      <c r="C27">
+        <v>2.362751552046499</v>
+      </c>
+      <c r="D27">
+        <v>8.944751552046499</v>
+      </c>
+      <c r="E27">
+        <v>-7.375</v>
+      </c>
+      <c r="F27">
+        <v>7.025</v>
+      </c>
+      <c r="G27">
+        <v>0.443</v>
+      </c>
+      <c r="H27">
+        <v>13.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.44</v>
+      </c>
+      <c r="K27">
+        <v>0.334</v>
+      </c>
+      <c r="L27">
+        <v>0.106</v>
+      </c>
+      <c r="M27">
+        <v>1.67757</v>
+      </c>
+      <c r="N27">
+        <v>-1.57157</v>
+      </c>
+      <c r="O27">
+        <v>-0.4400396000000001</v>
+      </c>
+      <c r="P27">
+        <v>-1.1315304</v>
+      </c>
+      <c r="Q27">
+        <v>-0.7975304000000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.07709213355482893</v>
+      </c>
+      <c r="T27">
+        <v>0.6474565039924516</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.01769225725305054</v>
+      </c>
+      <c r="W27">
+        <v>0.2345750889679715</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.06318663304660899</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1184628724081146</v>
+      </c>
+      <c r="C28">
+        <v>1.857186424486892</v>
+      </c>
+      <c r="D28">
+        <v>8.720186424486894</v>
+      </c>
+      <c r="E28">
+        <v>-7.093999999999999</v>
+      </c>
+      <c r="F28">
+        <v>7.306000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.443</v>
+      </c>
+      <c r="H28">
+        <v>13.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.44</v>
+      </c>
+      <c r="K28">
+        <v>0.334</v>
+      </c>
+      <c r="L28">
+        <v>0.106</v>
+      </c>
+      <c r="M28">
+        <v>1.7446728</v>
+      </c>
+      <c r="N28">
+        <v>-1.6386728</v>
+      </c>
+      <c r="O28">
+        <v>-0.4588283840000001</v>
+      </c>
+      <c r="P28">
+        <v>-1.179844416</v>
+      </c>
+      <c r="Q28">
+        <v>-0.845844416</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.07760959481908336</v>
+      </c>
+      <c r="T28">
+        <v>0.6562059162085658</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.0170117858202409</v>
+      </c>
+      <c r="W28">
+        <v>0.2347375855461265</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.06075637792943189</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1204628724081146</v>
+      </c>
+      <c r="C29">
+        <v>1.362620916261629</v>
+      </c>
+      <c r="D29">
+        <v>8.50662091626163</v>
+      </c>
+      <c r="E29">
+        <v>-6.813</v>
+      </c>
+      <c r="F29">
+        <v>7.587000000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.443</v>
+      </c>
+      <c r="H29">
+        <v>13.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.44</v>
+      </c>
+      <c r="K29">
+        <v>0.334</v>
+      </c>
+      <c r="L29">
+        <v>0.106</v>
+      </c>
+      <c r="M29">
+        <v>1.8117756</v>
+      </c>
+      <c r="N29">
+        <v>-1.7057756</v>
+      </c>
+      <c r="O29">
+        <v>-0.4776171680000001</v>
+      </c>
+      <c r="P29">
+        <v>-1.228158432</v>
+      </c>
+      <c r="Q29">
+        <v>-0.8941584320000002</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.07814123310427629</v>
+      </c>
+      <c r="T29">
+        <v>0.6651950383484092</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.0163817196787505</v>
+      </c>
+      <c r="W29">
+        <v>0.2348880453407144</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.05850614170982316</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1224628724081146</v>
+      </c>
+      <c r="C30">
+        <v>0.8782661742736719</v>
+      </c>
+      <c r="D30">
+        <v>8.303266174273674</v>
+      </c>
+      <c r="E30">
+        <v>-6.531999999999999</v>
+      </c>
+      <c r="F30">
+        <v>7.868000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.443</v>
+      </c>
+      <c r="H30">
+        <v>13.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.44</v>
+      </c>
+      <c r="K30">
+        <v>0.334</v>
+      </c>
+      <c r="L30">
+        <v>0.106</v>
+      </c>
+      <c r="M30">
+        <v>1.8788784</v>
+      </c>
+      <c r="N30">
+        <v>-1.7728784</v>
+      </c>
+      <c r="O30">
+        <v>-0.4964059520000001</v>
+      </c>
+      <c r="P30">
+        <v>-1.276472448</v>
+      </c>
+      <c r="Q30">
+        <v>-0.942472448</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.07868763911961346</v>
+      </c>
+      <c r="T30">
+        <v>0.6744338583254705</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.01579665826165227</v>
+      </c>
+      <c r="W30">
+        <v>0.2350277580071174</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.05641663664875818</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1244628724081146</v>
+      </c>
+      <c r="C31">
+        <v>0.403407015904218</v>
+      </c>
+      <c r="D31">
+        <v>8.109407015904218</v>
+      </c>
+      <c r="E31">
+        <v>-6.251000000000001</v>
+      </c>
+      <c r="F31">
+        <v>8.148999999999999</v>
+      </c>
+      <c r="G31">
+        <v>0.443</v>
+      </c>
+      <c r="H31">
+        <v>13.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.44</v>
+      </c>
+      <c r="K31">
+        <v>0.334</v>
+      </c>
+      <c r="L31">
+        <v>0.106</v>
+      </c>
+      <c r="M31">
+        <v>1.9459812</v>
+      </c>
+      <c r="N31">
+        <v>-1.8399812</v>
+      </c>
+      <c r="O31">
+        <v>-0.5151947360000001</v>
+      </c>
+      <c r="P31">
+        <v>-1.324786464</v>
+      </c>
+      <c r="Q31">
+        <v>-0.9907864639999997</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.07924943685369251</v>
+      </c>
+      <c r="T31">
+        <v>0.6839329267525897</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.01525194590780219</v>
+      </c>
+      <c r="W31">
+        <v>0.2351578353172168</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.05447123538500775</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1264628724081146</v>
+      </c>
+      <c r="C32">
+        <v>-0.06260647482765869</v>
+      </c>
+      <c r="D32">
+        <v>7.924393525172341</v>
+      </c>
+      <c r="E32">
+        <v>-5.970000000000001</v>
+      </c>
+      <c r="F32">
+        <v>8.43</v>
+      </c>
+      <c r="G32">
+        <v>0.443</v>
+      </c>
+      <c r="H32">
+        <v>13.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.44</v>
+      </c>
+      <c r="K32">
+        <v>0.334</v>
+      </c>
+      <c r="L32">
+        <v>0.106</v>
+      </c>
+      <c r="M32">
+        <v>2.013084</v>
+      </c>
+      <c r="N32">
+        <v>-1.907084</v>
+      </c>
+      <c r="O32">
+        <v>-0.5339835200000002</v>
+      </c>
+      <c r="P32">
+        <v>-1.37310048</v>
+      </c>
+      <c r="Q32">
+        <v>-1.03910048</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.07982728595160242</v>
+      </c>
+      <c r="T32">
+        <v>0.6937033971347696</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.01474354771087545</v>
+      </c>
+      <c r="W32">
+        <v>0.2352792408066429</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.05265552753884084</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1284628724081146</v>
+      </c>
+      <c r="C33">
+        <v>-0.5203662263801903</v>
+      </c>
+      <c r="D33">
+        <v>7.74763377361981</v>
+      </c>
+      <c r="E33">
+        <v>-5.689</v>
+      </c>
+      <c r="F33">
+        <v>8.711</v>
+      </c>
+      <c r="G33">
+        <v>0.443</v>
+      </c>
+      <c r="H33">
+        <v>13.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.44</v>
+      </c>
+      <c r="K33">
+        <v>0.334</v>
+      </c>
+      <c r="L33">
+        <v>0.106</v>
+      </c>
+      <c r="M33">
+        <v>2.0801868</v>
+      </c>
+      <c r="N33">
+        <v>-1.9741868</v>
+      </c>
+      <c r="O33">
+        <v>-0.5527723040000002</v>
+      </c>
+      <c r="P33">
+        <v>-1.421414496</v>
+      </c>
+      <c r="Q33">
+        <v>-1.087414496</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.0804218842987271</v>
+      </c>
+      <c r="T33">
+        <v>0.7037570695570127</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.0142679493976214</v>
+      </c>
+      <c r="W33">
+        <v>0.235392813683848</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.05095696213436207</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1304628724081146</v>
+      </c>
+      <c r="C34">
+        <v>-0.970412505862349</v>
+      </c>
+      <c r="D34">
+        <v>7.578587494137651</v>
+      </c>
+      <c r="E34">
+        <v>-5.407999999999999</v>
+      </c>
+      <c r="F34">
+        <v>8.992000000000001</v>
+      </c>
+      <c r="G34">
+        <v>0.443</v>
+      </c>
+      <c r="H34">
+        <v>13.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.44</v>
+      </c>
+      <c r="K34">
+        <v>0.334</v>
+      </c>
+      <c r="L34">
+        <v>0.106</v>
+      </c>
+      <c r="M34">
+        <v>2.1472896</v>
+      </c>
+      <c r="N34">
+        <v>-2.0412896</v>
+      </c>
+      <c r="O34">
+        <v>-0.5715610880000002</v>
+      </c>
+      <c r="P34">
+        <v>-1.469728512</v>
+      </c>
+      <c r="Q34">
+        <v>-1.135728512</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.0810339708325319</v>
+      </c>
+      <c r="T34">
+        <v>0.7141064382269687</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.01382207597894573</v>
+      </c>
+      <c r="W34">
+        <v>0.2354992882562278</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.04936455706766329</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1324628724081146</v>
+      </c>
+      <c r="C35">
+        <v>-1.413239434703818</v>
+      </c>
+      <c r="D35">
+        <v>7.416760565296184</v>
+      </c>
+      <c r="E35">
+        <v>-5.126999999999999</v>
+      </c>
+      <c r="F35">
+        <v>9.273000000000001</v>
+      </c>
+      <c r="G35">
+        <v>0.443</v>
+      </c>
+      <c r="H35">
+        <v>13.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.44</v>
+      </c>
+      <c r="K35">
+        <v>0.334</v>
+      </c>
+      <c r="L35">
+        <v>0.106</v>
+      </c>
+      <c r="M35">
+        <v>2.2143924</v>
+      </c>
+      <c r="N35">
+        <v>-2.1083924</v>
+      </c>
+      <c r="O35">
+        <v>-0.5903498720000002</v>
+      </c>
+      <c r="P35">
+        <v>-1.518042528</v>
+      </c>
+      <c r="Q35">
+        <v>-1.184042528</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.08166432860615178</v>
+      </c>
+      <c r="T35">
+        <v>0.7247647432751324</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.01340322519170495</v>
+      </c>
+      <c r="W35">
+        <v>0.2355993098242209</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.04786866139894619</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1344628724081146</v>
+      </c>
+      <c r="C36">
+        <v>-1.849299812436466</v>
+      </c>
+      <c r="D36">
+        <v>7.261700187563537</v>
+      </c>
+      <c r="E36">
+        <v>-4.845999999999998</v>
+      </c>
+      <c r="F36">
+        <v>9.554000000000002</v>
+      </c>
+      <c r="G36">
+        <v>0.443</v>
+      </c>
+      <c r="H36">
+        <v>13.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.44</v>
+      </c>
+      <c r="K36">
+        <v>0.334</v>
+      </c>
+      <c r="L36">
+        <v>0.106</v>
+      </c>
+      <c r="M36">
+        <v>2.281495200000001</v>
+      </c>
+      <c r="N36">
+        <v>-2.175495200000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.6091386560000003</v>
+      </c>
+      <c r="P36">
+        <v>-1.566356544</v>
+      </c>
+      <c r="Q36">
+        <v>-1.232356544</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.08231378813048743</v>
+      </c>
+      <c r="T36">
+        <v>0.7357460272641496</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.01300901268606657</v>
+      </c>
+      <c r="W36">
+        <v>0.2356934477705673</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.04646075959309481</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1364628724081146</v>
+      </c>
+      <c r="C37">
+        <v>-2.279009347769774</v>
+      </c>
+      <c r="D37">
+        <v>7.112990652230227</v>
+      </c>
+      <c r="E37">
+        <v>-4.565</v>
+      </c>
+      <c r="F37">
+        <v>9.835000000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.443</v>
+      </c>
+      <c r="H37">
+        <v>13.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.44</v>
+      </c>
+      <c r="K37">
+        <v>0.334</v>
+      </c>
+      <c r="L37">
+        <v>0.106</v>
+      </c>
+      <c r="M37">
+        <v>2.348598</v>
+      </c>
+      <c r="N37">
+        <v>-2.242598000000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.6279274400000002</v>
+      </c>
+      <c r="P37">
+        <v>-1.61467056</v>
+      </c>
+      <c r="Q37">
+        <v>-1.28067056</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.08298323102480261</v>
+      </c>
+      <c r="T37">
+        <v>0.7470651969143673</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.01263732660932181</v>
+      </c>
+      <c r="W37">
+        <v>0.235782206405694</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.04513330931900639</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1384628724081146</v>
+      </c>
+      <c r="C38">
+        <v>-2.702750380219708</v>
+      </c>
+      <c r="D38">
+        <v>6.970249619780292</v>
+      </c>
+      <c r="E38">
+        <v>-4.284000000000001</v>
+      </c>
+      <c r="F38">
+        <v>10.116</v>
+      </c>
+      <c r="G38">
+        <v>0.443</v>
+      </c>
+      <c r="H38">
+        <v>13.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.44</v>
+      </c>
+      <c r="K38">
+        <v>0.334</v>
+      </c>
+      <c r="L38">
+        <v>0.106</v>
+      </c>
+      <c r="M38">
+        <v>2.4157008</v>
+      </c>
+      <c r="N38">
+        <v>-2.3097008</v>
+      </c>
+      <c r="O38">
+        <v>-0.6467162240000002</v>
+      </c>
+      <c r="P38">
+        <v>-1.662984576</v>
+      </c>
+      <c r="Q38">
+        <v>-1.328984576</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.08367359400956514</v>
+      </c>
+      <c r="T38">
+        <v>0.7587380906161542</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.01228628975906288</v>
+      </c>
+      <c r="W38">
+        <v>0.2358660340055358</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.04387960628236731</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1404628724081146</v>
+      </c>
+      <c r="C39">
+        <v>-3.12087516244697</v>
+      </c>
+      <c r="D39">
+        <v>6.83312483755303</v>
+      </c>
+      <c r="E39">
+        <v>-4.003</v>
+      </c>
+      <c r="F39">
+        <v>10.397</v>
+      </c>
+      <c r="G39">
+        <v>0.443</v>
+      </c>
+      <c r="H39">
+        <v>13.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.44</v>
+      </c>
+      <c r="K39">
+        <v>0.334</v>
+      </c>
+      <c r="L39">
+        <v>0.106</v>
+      </c>
+      <c r="M39">
+        <v>2.4828036</v>
+      </c>
+      <c r="N39">
+        <v>-2.3768036</v>
+      </c>
+      <c r="O39">
+        <v>-0.6655050080000001</v>
+      </c>
+      <c r="P39">
+        <v>-1.711298592</v>
+      </c>
+      <c r="Q39">
+        <v>-1.377298592</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.08438587327955824</v>
+      </c>
+      <c r="T39">
+        <v>0.7707815523719662</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.0119542278736828</v>
+      </c>
+      <c r="W39">
+        <v>0.2359453303837646</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.04269367097743848</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1424628724081146</v>
+      </c>
+      <c r="C40">
+        <v>-3.533708762632224</v>
+      </c>
+      <c r="D40">
+        <v>6.701291237367777</v>
+      </c>
+      <c r="E40">
+        <v>-3.722</v>
+      </c>
+      <c r="F40">
+        <v>10.678</v>
+      </c>
+      <c r="G40">
+        <v>0.443</v>
+      </c>
+      <c r="H40">
+        <v>13.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.44</v>
+      </c>
+      <c r="K40">
+        <v>0.334</v>
+      </c>
+      <c r="L40">
+        <v>0.106</v>
+      </c>
+      <c r="M40">
+        <v>2.5499064</v>
+      </c>
+      <c r="N40">
+        <v>-2.4439064</v>
+      </c>
+      <c r="O40">
+        <v>-0.6842937920000002</v>
+      </c>
+      <c r="P40">
+        <v>-1.759612608</v>
+      </c>
+      <c r="Q40">
+        <v>-1.425612608</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.08512112930019627</v>
+      </c>
+      <c r="T40">
+        <v>0.7832135128940947</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.01163964292963851</v>
+      </c>
+      <c r="W40">
+        <v>0.2360204532684023</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.04157015332013747</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1444628724081146</v>
+      </c>
+      <c r="C41">
+        <v>-3.941551637232198</v>
+      </c>
+      <c r="D41">
+        <v>6.574448362767804</v>
+      </c>
+      <c r="E41">
+        <v>-3.440999999999999</v>
+      </c>
+      <c r="F41">
+        <v>10.959</v>
+      </c>
+      <c r="G41">
+        <v>0.443</v>
+      </c>
+      <c r="H41">
+        <v>13.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.44</v>
+      </c>
+      <c r="K41">
+        <v>0.334</v>
+      </c>
+      <c r="L41">
+        <v>0.106</v>
+      </c>
+      <c r="M41">
+        <v>2.6170092</v>
+      </c>
+      <c r="N41">
+        <v>-2.511009200000001</v>
+      </c>
+      <c r="O41">
+        <v>-0.7030825760000002</v>
+      </c>
+      <c r="P41">
+        <v>-1.807926624</v>
+      </c>
+      <c r="Q41">
+        <v>-1.473926624</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.08588049207560933</v>
+      </c>
+      <c r="T41">
+        <v>0.7960530786792438</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.01134119054682727</v>
+      </c>
+      <c r="W41">
+        <v>0.2360917236974177</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.04050425195295448</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1464628724081146</v>
+      </c>
+      <c r="C42">
+        <v>-4.344681916978892</v>
+      </c>
+      <c r="D42">
+        <v>6.45231808302111</v>
+      </c>
+      <c r="E42">
+        <v>-3.159999999999998</v>
+      </c>
+      <c r="F42">
+        <v>11.24</v>
+      </c>
+      <c r="G42">
+        <v>0.443</v>
+      </c>
+      <c r="H42">
+        <v>13.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.44</v>
+      </c>
+      <c r="K42">
+        <v>0.334</v>
+      </c>
+      <c r="L42">
+        <v>0.106</v>
+      </c>
+      <c r="M42">
+        <v>2.684112000000001</v>
+      </c>
+      <c r="N42">
+        <v>-2.578112000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.7218713600000003</v>
+      </c>
+      <c r="P42">
+        <v>-1.856240640000001</v>
+      </c>
+      <c r="Q42">
+        <v>-1.522240640000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.08666516694353615</v>
+      </c>
+      <c r="T42">
+        <v>0.8093206299905645</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.01105766078315659</v>
+      </c>
+      <c r="W42">
+        <v>0.2361594306049822</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.03949164565413066</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1484628724081146</v>
+      </c>
+      <c r="C43">
+        <v>-4.74335744273037</v>
+      </c>
+      <c r="D43">
+        <v>6.334642557269631</v>
+      </c>
+      <c r="E43">
+        <v>-2.879</v>
+      </c>
+      <c r="F43">
+        <v>11.521</v>
+      </c>
+      <c r="G43">
+        <v>0.443</v>
+      </c>
+      <c r="H43">
+        <v>13.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.44</v>
+      </c>
+      <c r="K43">
+        <v>0.334</v>
+      </c>
+      <c r="L43">
+        <v>0.106</v>
+      </c>
+      <c r="M43">
+        <v>2.751214800000001</v>
+      </c>
+      <c r="N43">
+        <v>-2.645214800000001</v>
+      </c>
+      <c r="O43">
+        <v>-0.7406601440000002</v>
+      </c>
+      <c r="P43">
+        <v>-1.904554656</v>
+      </c>
+      <c r="Q43">
+        <v>-1.570554656</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.08747644095952829</v>
+      </c>
+      <c r="T43">
+        <v>0.8230379288039639</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.01078796173966496</v>
+      </c>
+      <c r="W43">
+        <v>0.236223834736568</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.03852843478451773</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1504628724081146</v>
+      </c>
+      <c r="C44">
+        <v>-5.137817582536147</v>
+      </c>
+      <c r="D44">
+        <v>6.221182417463853</v>
+      </c>
+      <c r="E44">
+        <v>-2.598000000000001</v>
+      </c>
+      <c r="F44">
+        <v>11.802</v>
+      </c>
+      <c r="G44">
+        <v>0.443</v>
+      </c>
+      <c r="H44">
+        <v>13.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.44</v>
+      </c>
+      <c r="K44">
+        <v>0.334</v>
+      </c>
+      <c r="L44">
+        <v>0.106</v>
+      </c>
+      <c r="M44">
+        <v>2.8183176</v>
+      </c>
+      <c r="N44">
+        <v>-2.7123176</v>
+      </c>
+      <c r="O44">
+        <v>-0.7594489280000001</v>
+      </c>
+      <c r="P44">
+        <v>-1.952868672</v>
+      </c>
+      <c r="Q44">
+        <v>-1.618868672</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.08831568994158913</v>
+      </c>
+      <c r="T44">
+        <v>0.8372282379212737</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.01053110550776818</v>
+      </c>
+      <c r="W44">
+        <v>0.236285172004745</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.03761109109917204</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1524628724081146</v>
+      </c>
+      <c r="C45">
+        <v>-5.528284856865204</v>
+      </c>
+      <c r="D45">
+        <v>6.111715143134797</v>
+      </c>
+      <c r="E45">
+        <v>-2.317</v>
+      </c>
+      <c r="F45">
+        <v>12.083</v>
+      </c>
+      <c r="G45">
+        <v>0.443</v>
+      </c>
+      <c r="H45">
+        <v>13.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.44</v>
+      </c>
+      <c r="K45">
+        <v>0.334</v>
+      </c>
+      <c r="L45">
+        <v>0.106</v>
+      </c>
+      <c r="M45">
+        <v>2.8854204</v>
+      </c>
+      <c r="N45">
+        <v>-2.7794204</v>
+      </c>
+      <c r="O45">
+        <v>-0.7782377120000001</v>
+      </c>
+      <c r="P45">
+        <v>-2.001182688</v>
+      </c>
+      <c r="Q45">
+        <v>-1.667182688</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.08918438625635383</v>
+      </c>
+      <c r="T45">
+        <v>0.8519164526216467</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.01028619607735497</v>
+      </c>
+      <c r="W45">
+        <v>0.2363436563767277</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.03673641456198196</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1544628724081146</v>
+      </c>
+      <c r="C46">
+        <v>-5.914966395216936</v>
+      </c>
+      <c r="D46">
+        <v>6.006033604783065</v>
+      </c>
+      <c r="E46">
+        <v>-2.036</v>
+      </c>
+      <c r="F46">
+        <v>12.364</v>
+      </c>
+      <c r="G46">
+        <v>0.443</v>
+      </c>
+      <c r="H46">
+        <v>13.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.44</v>
+      </c>
+      <c r="K46">
+        <v>0.334</v>
+      </c>
+      <c r="L46">
+        <v>0.106</v>
+      </c>
+      <c r="M46">
+        <v>2.9525232</v>
+      </c>
+      <c r="N46">
+        <v>-2.8465232</v>
+      </c>
+      <c r="O46">
+        <v>-0.7970264960000002</v>
+      </c>
+      <c r="P46">
+        <v>-2.049496704</v>
+      </c>
+      <c r="Q46">
+        <v>-1.715496704</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.09008410743950301</v>
+      </c>
+      <c r="T46">
+        <v>0.8671292464184619</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.01005241889377872</v>
+      </c>
+      <c r="W46">
+        <v>0.2363994823681657</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.03590149604920967</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1564628724081146</v>
+      </c>
+      <c r="C47">
+        <v>-6.298055244177738</v>
+      </c>
+      <c r="D47">
+        <v>5.903944755822264</v>
+      </c>
+      <c r="E47">
+        <v>-1.754999999999999</v>
+      </c>
+      <c r="F47">
+        <v>12.645</v>
+      </c>
+      <c r="G47">
+        <v>0.443</v>
+      </c>
+      <c r="H47">
+        <v>13.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.44</v>
+      </c>
+      <c r="K47">
+        <v>0.334</v>
+      </c>
+      <c r="L47">
+        <v>0.106</v>
+      </c>
+      <c r="M47">
+        <v>3.019626000000001</v>
+      </c>
+      <c r="N47">
+        <v>-2.913626000000001</v>
+      </c>
+      <c r="O47">
+        <v>-0.8158152800000003</v>
+      </c>
+      <c r="P47">
+        <v>-2.09781072</v>
+      </c>
+      <c r="Q47">
+        <v>-1.76381072</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.0910165457565849</v>
+      </c>
+      <c r="T47">
+        <v>0.8828952327169795</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.009829031807250298</v>
+      </c>
+      <c r="W47">
+        <v>0.2364528272044286</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.03510368502589389</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1584628724081146</v>
+      </c>
+      <c r="C48">
+        <v>-6.677731544303422</v>
+      </c>
+      <c r="D48">
+        <v>5.80526845569658</v>
+      </c>
+      <c r="E48">
+        <v>-1.473999999999998</v>
+      </c>
+      <c r="F48">
+        <v>12.926</v>
+      </c>
+      <c r="G48">
+        <v>0.443</v>
+      </c>
+      <c r="H48">
+        <v>13.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.44</v>
+      </c>
+      <c r="K48">
+        <v>0.334</v>
+      </c>
+      <c r="L48">
+        <v>0.106</v>
+      </c>
+      <c r="M48">
+        <v>3.086728800000001</v>
+      </c>
+      <c r="N48">
+        <v>-2.980728800000001</v>
+      </c>
+      <c r="O48">
+        <v>-0.8346040640000003</v>
+      </c>
+      <c r="P48">
+        <v>-2.146124736000001</v>
+      </c>
+      <c r="Q48">
+        <v>-1.812124736000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.09198351882615127</v>
+      </c>
+      <c r="T48">
+        <v>0.8992451444339605</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.009615357202744857</v>
+      </c>
+      <c r="W48">
+        <v>0.2365038526999845</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.0343405614383745</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1604628724081146</v>
+      </c>
+      <c r="C49">
+        <v>-7.054163590921931</v>
+      </c>
+      <c r="D49">
+        <v>5.70983640907807</v>
+      </c>
+      <c r="E49">
+        <v>-1.193</v>
+      </c>
+      <c r="F49">
+        <v>13.207</v>
+      </c>
+      <c r="G49">
+        <v>0.443</v>
+      </c>
+      <c r="H49">
+        <v>13.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.44</v>
+      </c>
+      <c r="K49">
+        <v>0.334</v>
+      </c>
+      <c r="L49">
+        <v>0.106</v>
+      </c>
+      <c r="M49">
+        <v>3.1538316</v>
+      </c>
+      <c r="N49">
+        <v>-3.0478316</v>
+      </c>
+      <c r="O49">
+        <v>-0.8533928480000001</v>
+      </c>
+      <c r="P49">
+        <v>-2.194438752</v>
+      </c>
+      <c r="Q49">
+        <v>-1.860438752</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.09298698144551262</v>
+      </c>
+      <c r="T49">
+        <v>0.9162120339515825</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.009410775134601352</v>
+      </c>
+      <c r="W49">
+        <v>0.2365527068978572</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.03360991119500478</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1624628724081146</v>
+      </c>
+      <c r="C50">
+        <v>-7.427508791997876</v>
+      </c>
+      <c r="D50">
+        <v>5.617491208002124</v>
+      </c>
+      <c r="E50">
+        <v>-0.9120000000000008</v>
+      </c>
+      <c r="F50">
+        <v>13.488</v>
+      </c>
+      <c r="G50">
+        <v>0.443</v>
+      </c>
+      <c r="H50">
+        <v>13.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.44</v>
+      </c>
+      <c r="K50">
+        <v>0.334</v>
+      </c>
+      <c r="L50">
+        <v>0.106</v>
+      </c>
+      <c r="M50">
+        <v>3.2209344</v>
+      </c>
+      <c r="N50">
+        <v>-3.1149344</v>
+      </c>
+      <c r="O50">
+        <v>-0.8721816320000001</v>
+      </c>
+      <c r="P50">
+        <v>-2.242752768</v>
+      </c>
+      <c r="Q50">
+        <v>-1.908752768</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.09402903878100324</v>
+      </c>
+      <c r="T50">
+        <v>0.933831496142959</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.009214717319297157</v>
+      </c>
+      <c r="W50">
+        <v>0.2365995255041519</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.03290970471177557</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1644628724081146</v>
+      </c>
+      <c r="C51">
+        <v>-7.797914534527113</v>
+      </c>
+      <c r="D51">
+        <v>5.528085465472888</v>
+      </c>
+      <c r="E51">
+        <v>-0.6310000000000002</v>
+      </c>
+      <c r="F51">
+        <v>13.769</v>
+      </c>
+      <c r="G51">
+        <v>0.443</v>
+      </c>
+      <c r="H51">
+        <v>13.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.44</v>
+      </c>
+      <c r="K51">
+        <v>0.334</v>
+      </c>
+      <c r="L51">
+        <v>0.106</v>
+      </c>
+      <c r="M51">
+        <v>3.2880372</v>
+      </c>
+      <c r="N51">
+        <v>-3.1820372</v>
+      </c>
+      <c r="O51">
+        <v>-0.8909704160000002</v>
+      </c>
+      <c r="P51">
+        <v>-2.291066784</v>
+      </c>
+      <c r="Q51">
+        <v>-1.957066784</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.09511196111004253</v>
+      </c>
+      <c r="T51">
+        <v>0.9521419176359582</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.009026661863801296</v>
+      </c>
+      <c r="W51">
+        <v>0.2366444331469243</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.03223807808500456</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1664628724081146</v>
+      </c>
+      <c r="C52">
+        <v>-8.165518969492364</v>
+      </c>
+      <c r="D52">
+        <v>5.441481030507637</v>
+      </c>
+      <c r="E52">
+        <v>-0.3499999999999996</v>
+      </c>
+      <c r="F52">
+        <v>14.05</v>
+      </c>
+      <c r="G52">
+        <v>0.443</v>
+      </c>
+      <c r="H52">
+        <v>13.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.44</v>
+      </c>
+      <c r="K52">
+        <v>0.334</v>
+      </c>
+      <c r="L52">
+        <v>0.106</v>
+      </c>
+      <c r="M52">
+        <v>3.35514</v>
+      </c>
+      <c r="N52">
+        <v>-3.249140000000001</v>
+      </c>
+      <c r="O52">
+        <v>-0.9097592000000002</v>
+      </c>
+      <c r="P52">
+        <v>-2.3393808</v>
+      </c>
+      <c r="Q52">
+        <v>-2.0053808</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.0962382003322434</v>
+      </c>
+      <c r="T52">
+        <v>0.9711847559886775</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.008846128626525271</v>
+      </c>
+      <c r="W52">
+        <v>0.2366875444839858</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.03159331652330455</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1684628724081146</v>
+      </c>
+      <c r="C53">
+        <v>-8.530451724172989</v>
+      </c>
+      <c r="D53">
+        <v>5.357548275827012</v>
+      </c>
+      <c r="E53">
+        <v>-0.06899999999999906</v>
+      </c>
+      <c r="F53">
+        <v>14.331</v>
+      </c>
+      <c r="G53">
+        <v>0.443</v>
+      </c>
+      <c r="H53">
+        <v>13.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.44</v>
+      </c>
+      <c r="K53">
+        <v>0.334</v>
+      </c>
+      <c r="L53">
+        <v>0.106</v>
+      </c>
+      <c r="M53">
+        <v>3.422242800000001</v>
+      </c>
+      <c r="N53">
+        <v>-3.316242800000001</v>
+      </c>
+      <c r="O53">
+        <v>-0.9285479840000003</v>
+      </c>
+      <c r="P53">
+        <v>-2.387694816000001</v>
+      </c>
+      <c r="Q53">
+        <v>-2.053694816000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.09741040850228919</v>
+      </c>
+      <c r="T53">
+        <v>0.991004853049671</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.008672675124044382</v>
+      </c>
+      <c r="W53">
+        <v>0.2367289651803782</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.03097383972872991</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1704628724081146</v>
+      </c>
+      <c r="C54">
+        <v>-8.892834549533511</v>
+      </c>
+      <c r="D54">
+        <v>5.276165450466491</v>
+      </c>
+      <c r="E54">
+        <v>0.2120000000000015</v>
+      </c>
+      <c r="F54">
+        <v>14.612</v>
+      </c>
+      <c r="G54">
+        <v>0.443</v>
+      </c>
+      <c r="H54">
+        <v>13.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.44</v>
+      </c>
+      <c r="K54">
+        <v>0.334</v>
+      </c>
+      <c r="L54">
+        <v>0.106</v>
+      </c>
+      <c r="M54">
+        <v>3.4893456</v>
+      </c>
+      <c r="N54">
+        <v>-3.383345600000001</v>
+      </c>
+      <c r="O54">
+        <v>-0.9473367680000002</v>
+      </c>
+      <c r="P54">
+        <v>-2.436008832000001</v>
+      </c>
+      <c r="Q54">
+        <v>-2.102008832000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.09863145867942022</v>
+      </c>
+      <c r="T54">
+        <v>1.011650787488206</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.008505892910120452</v>
+      </c>
+      <c r="W54">
+        <v>0.2367687927730632</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.03037818896471589</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1724628724081146</v>
+      </c>
+      <c r="C55">
+        <v>-9.252781909490832</v>
+      </c>
+      <c r="D55">
+        <v>5.19721809050917</v>
+      </c>
+      <c r="E55">
+        <v>0.4930000000000003</v>
+      </c>
+      <c r="F55">
+        <v>14.893</v>
+      </c>
+      <c r="G55">
+        <v>0.443</v>
+      </c>
+      <c r="H55">
+        <v>13.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.44</v>
+      </c>
+      <c r="K55">
+        <v>0.334</v>
+      </c>
+      <c r="L55">
+        <v>0.106</v>
+      </c>
+      <c r="M55">
+        <v>3.5564484</v>
+      </c>
+      <c r="N55">
+        <v>-3.4504484</v>
+      </c>
+      <c r="O55">
+        <v>-0.9661255520000002</v>
+      </c>
+      <c r="P55">
+        <v>-2.484322848</v>
+      </c>
+      <c r="Q55">
+        <v>-2.150322848</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.0999044684385568</v>
+      </c>
+      <c r="T55">
+        <v>1.03317527232838</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.008345404364646482</v>
+      </c>
+      <c r="W55">
+        <v>0.2368071174377224</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.02980501558802306</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1744628724081146</v>
+      </c>
+      <c r="C56">
+        <v>-9.61040151805808</v>
+      </c>
+      <c r="D56">
+        <v>5.120598481941922</v>
+      </c>
+      <c r="E56">
+        <v>0.7740000000000009</v>
+      </c>
+      <c r="F56">
+        <v>15.174</v>
+      </c>
+      <c r="G56">
+        <v>0.443</v>
+      </c>
+      <c r="H56">
+        <v>13.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.44</v>
+      </c>
+      <c r="K56">
+        <v>0.334</v>
+      </c>
+      <c r="L56">
+        <v>0.106</v>
+      </c>
+      <c r="M56">
+        <v>3.623551200000001</v>
+      </c>
+      <c r="N56">
+        <v>-3.517551200000001</v>
+      </c>
+      <c r="O56">
+        <v>-0.9849143360000002</v>
+      </c>
+      <c r="P56">
+        <v>-2.532636864000001</v>
+      </c>
+      <c r="Q56">
+        <v>-2.198636864</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1012328264480906</v>
+      </c>
+      <c r="T56">
+        <v>1.055635604335519</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.00819085983937525</v>
+      </c>
+      <c r="W56">
+        <v>0.2368440226703572</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.02925307085491158</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1764628724081146</v>
+      </c>
+      <c r="C57">
+        <v>-9.965794829665896</v>
+      </c>
+      <c r="D57">
+        <v>5.046205170334106</v>
+      </c>
+      <c r="E57">
+        <v>1.055000000000001</v>
+      </c>
+      <c r="F57">
+        <v>15.455</v>
+      </c>
+      <c r="G57">
+        <v>0.443</v>
+      </c>
+      <c r="H57">
+        <v>13.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.44</v>
+      </c>
+      <c r="K57">
+        <v>0.334</v>
+      </c>
+      <c r="L57">
+        <v>0.106</v>
+      </c>
+      <c r="M57">
+        <v>3.690654000000001</v>
+      </c>
+      <c r="N57">
+        <v>-3.584654000000001</v>
+      </c>
+      <c r="O57">
+        <v>-1.00370312</v>
+      </c>
+      <c r="P57">
+        <v>-2.580950880000001</v>
+      </c>
+      <c r="Q57">
+        <v>-2.24695088</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1026202225913816</v>
+      </c>
+      <c r="T57">
+        <v>1.079094173320753</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.008041935115022972</v>
+      </c>
+      <c r="W57">
+        <v>0.2368795858945325</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.02872119683936769</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1784628724081146</v>
+      </c>
+      <c r="C58">
+        <v>-10.31905748735474</v>
+      </c>
+      <c r="D58">
+        <v>4.973942512645263</v>
+      </c>
+      <c r="E58">
+        <v>1.336000000000002</v>
+      </c>
+      <c r="F58">
+        <v>15.736</v>
+      </c>
+      <c r="G58">
+        <v>0.443</v>
+      </c>
+      <c r="H58">
+        <v>13.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.44</v>
+      </c>
+      <c r="K58">
+        <v>0.334</v>
+      </c>
+      <c r="L58">
+        <v>0.106</v>
+      </c>
+      <c r="M58">
+        <v>3.757756800000001</v>
+      </c>
+      <c r="N58">
+        <v>-3.651756800000001</v>
+      </c>
+      <c r="O58">
+        <v>-1.022491904</v>
+      </c>
+      <c r="P58">
+        <v>-2.629264896</v>
+      </c>
+      <c r="Q58">
+        <v>-2.295264896</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1040706821957311</v>
+      </c>
+      <c r="T58">
+        <v>1.103619040896225</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.007898329130826134</v>
+      </c>
+      <c r="W58">
+        <v>0.2369138790035587</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.02820831832437898</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1804628724081146</v>
+      </c>
+      <c r="C59">
+        <v>-10.67027973300166</v>
+      </c>
+      <c r="D59">
+        <v>4.903720266998345</v>
+      </c>
+      <c r="E59">
+        <v>1.617000000000003</v>
+      </c>
+      <c r="F59">
+        <v>16.017</v>
+      </c>
+      <c r="G59">
+        <v>0.443</v>
+      </c>
+      <c r="H59">
+        <v>13.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.44</v>
+      </c>
+      <c r="K59">
+        <v>0.334</v>
+      </c>
+      <c r="L59">
+        <v>0.106</v>
+      </c>
+      <c r="M59">
+        <v>3.824859600000001</v>
+      </c>
+      <c r="N59">
+        <v>-3.718859600000001</v>
+      </c>
+      <c r="O59">
+        <v>-1.041280688</v>
+      </c>
+      <c r="P59">
+        <v>-2.677578912</v>
+      </c>
+      <c r="Q59">
+        <v>-2.343578912</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1055886050374923</v>
+      </c>
+      <c r="T59">
+        <v>1.129284599986834</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.007759761953092342</v>
+      </c>
+      <c r="W59">
+        <v>0.2369469688456016</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.02771343554675831</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1824628724081145</v>
+      </c>
+      <c r="C60">
+        <v>-11.01954678328125</v>
+      </c>
+      <c r="D60">
+        <v>4.835453216718746</v>
+      </c>
+      <c r="E60">
+        <v>1.897999999999998</v>
+      </c>
+      <c r="F60">
+        <v>16.298</v>
+      </c>
+      <c r="G60">
+        <v>0.443</v>
+      </c>
+      <c r="H60">
+        <v>13.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.44</v>
+      </c>
+      <c r="K60">
+        <v>0.334</v>
+      </c>
+      <c r="L60">
+        <v>0.106</v>
+      </c>
+      <c r="M60">
+        <v>3.8919624</v>
+      </c>
+      <c r="N60">
+        <v>-3.7859624</v>
+      </c>
+      <c r="O60">
+        <v>-1.060069472</v>
+      </c>
+      <c r="P60">
+        <v>-2.725892927999999</v>
+      </c>
+      <c r="Q60">
+        <v>-2.391892927999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1071788099193373</v>
+      </c>
+      <c r="T60">
+        <v>1.156172328557949</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.007625972953901096</v>
+      </c>
+      <c r="W60">
+        <v>0.2369789176586084</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.02723561769250393</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1844628724081146</v>
+      </c>
+      <c r="C61">
+        <v>-11.36693917465428</v>
+      </c>
+      <c r="D61">
+        <v>4.769060825345726</v>
+      </c>
+      <c r="E61">
+        <v>2.179</v>
+      </c>
+      <c r="F61">
+        <v>16.579</v>
+      </c>
+      <c r="G61">
+        <v>0.443</v>
+      </c>
+      <c r="H61">
+        <v>13.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.44</v>
+      </c>
+      <c r="K61">
+        <v>0.334</v>
+      </c>
+      <c r="L61">
+        <v>0.106</v>
+      </c>
+      <c r="M61">
+        <v>3.9590652</v>
+      </c>
+      <c r="N61">
+        <v>-3.853065200000001</v>
+      </c>
+      <c r="O61">
+        <v>-1.078858256</v>
+      </c>
+      <c r="P61">
+        <v>-2.774206944</v>
+      </c>
+      <c r="Q61">
+        <v>-2.440206944</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1088465857710285</v>
+      </c>
+      <c r="T61">
+        <v>1.184371653644729</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.007496719175021416</v>
+      </c>
+      <c r="W61">
+        <v>0.2370097834610049</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.02677399705364791</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1864628724081146</v>
+      </c>
+      <c r="C62">
+        <v>-11.71253308032021</v>
+      </c>
+      <c r="D62">
+        <v>4.704466919679787</v>
+      </c>
+      <c r="E62">
+        <v>2.459999999999999</v>
+      </c>
+      <c r="F62">
+        <v>16.86</v>
+      </c>
+      <c r="G62">
+        <v>0.443</v>
+      </c>
+      <c r="H62">
+        <v>13.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.44</v>
+      </c>
+      <c r="K62">
+        <v>0.334</v>
+      </c>
+      <c r="L62">
+        <v>0.106</v>
+      </c>
+      <c r="M62">
+        <v>4.026168</v>
+      </c>
+      <c r="N62">
+        <v>-3.920168</v>
+      </c>
+      <c r="O62">
+        <v>-1.09764704</v>
+      </c>
+      <c r="P62">
+        <v>-2.82252096</v>
+      </c>
+      <c r="Q62">
+        <v>-2.48852096</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1105977504153042</v>
+      </c>
+      <c r="T62">
+        <v>1.213980944985847</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.007371773855437725</v>
+      </c>
+      <c r="W62">
+        <v>0.2370396204033215</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.02632776376942036</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1884628724081146</v>
+      </c>
+      <c r="C63">
+        <v>-12.05640060175667</v>
+      </c>
+      <c r="D63">
+        <v>4.641599398243327</v>
+      </c>
+      <c r="E63">
+        <v>2.741000000000001</v>
+      </c>
+      <c r="F63">
+        <v>17.141</v>
+      </c>
+      <c r="G63">
+        <v>0.443</v>
+      </c>
+      <c r="H63">
+        <v>13.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.44</v>
+      </c>
+      <c r="K63">
+        <v>0.334</v>
+      </c>
+      <c r="L63">
+        <v>0.106</v>
+      </c>
+      <c r="M63">
+        <v>4.093270800000001</v>
+      </c>
+      <c r="N63">
+        <v>-3.987270800000001</v>
+      </c>
+      <c r="O63">
+        <v>-1.116435824</v>
+      </c>
+      <c r="P63">
+        <v>-2.870834976000001</v>
+      </c>
+      <c r="Q63">
+        <v>-2.536834976000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.112438718374671</v>
+      </c>
+      <c r="T63">
+        <v>1.245108661523946</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.007250925103709237</v>
+      </c>
+      <c r="W63">
+        <v>0.2370684790852342</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.02589616108467585</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1904628724081146</v>
+      </c>
+      <c r="C64">
+        <v>-12.39861003719125</v>
+      </c>
+      <c r="D64">
+        <v>4.580389962808746</v>
+      </c>
+      <c r="E64">
+        <v>3.022</v>
+      </c>
+      <c r="F64">
+        <v>17.422</v>
+      </c>
+      <c r="G64">
+        <v>0.443</v>
+      </c>
+      <c r="H64">
+        <v>13.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.44</v>
+      </c>
+      <c r="K64">
+        <v>0.334</v>
+      </c>
+      <c r="L64">
+        <v>0.106</v>
+      </c>
+      <c r="M64">
+        <v>4.160373600000001</v>
+      </c>
+      <c r="N64">
+        <v>-4.054373600000001</v>
+      </c>
+      <c r="O64">
+        <v>-1.135224608</v>
+      </c>
+      <c r="P64">
+        <v>-2.919148992</v>
+      </c>
+      <c r="Q64">
+        <v>-2.585148992</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1143765793845308</v>
+      </c>
+      <c r="T64">
+        <v>1.27787467893247</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.007133974698810702</v>
+      </c>
+      <c r="W64">
+        <v>0.237096406841924</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.02547848106718109</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1924628724081146</v>
+      </c>
+      <c r="C65">
+        <v>-12.73922612910764</v>
+      </c>
+      <c r="D65">
+        <v>4.520773870892364</v>
+      </c>
+      <c r="E65">
+        <v>3.302999999999999</v>
+      </c>
+      <c r="F65">
+        <v>17.703</v>
+      </c>
+      <c r="G65">
+        <v>0.443</v>
+      </c>
+      <c r="H65">
+        <v>13.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.44</v>
+      </c>
+      <c r="K65">
+        <v>0.334</v>
+      </c>
+      <c r="L65">
+        <v>0.106</v>
+      </c>
+      <c r="M65">
+        <v>4.2274764</v>
+      </c>
+      <c r="N65">
+        <v>-4.121476400000001</v>
+      </c>
+      <c r="O65">
+        <v>-1.154013392</v>
+      </c>
+      <c r="P65">
+        <v>-2.967463008</v>
+      </c>
+      <c r="Q65">
+        <v>-2.633463008</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1164191896381667</v>
+      </c>
+      <c r="T65">
+        <v>1.312411832417132</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.007020737005178786</v>
+      </c>
+      <c r="W65">
+        <v>0.2371234480031633</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.0250740607327814</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1944628724081146</v>
+      </c>
+      <c r="C66">
+        <v>-13.07831029267157</v>
+      </c>
+      <c r="D66">
+        <v>4.462689707328436</v>
+      </c>
+      <c r="E66">
+        <v>3.584000000000001</v>
+      </c>
+      <c r="F66">
+        <v>17.984</v>
+      </c>
+      <c r="G66">
+        <v>0.443</v>
+      </c>
+      <c r="H66">
+        <v>13.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.44</v>
+      </c>
+      <c r="K66">
+        <v>0.334</v>
+      </c>
+      <c r="L66">
+        <v>0.106</v>
+      </c>
+      <c r="M66">
+        <v>4.2945792</v>
+      </c>
+      <c r="N66">
+        <v>-4.1885792</v>
+      </c>
+      <c r="O66">
+        <v>-1.172802176</v>
+      </c>
+      <c r="P66">
+        <v>-3.015777024</v>
+      </c>
+      <c r="Q66">
+        <v>-2.681777024</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1185752782392269</v>
+      </c>
+      <c r="T66">
+        <v>1.348867716650941</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.006911037989472867</v>
+      </c>
+      <c r="W66">
+        <v>0.2371496441281139</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.02468227853383165</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1964628724081146</v>
+      </c>
+      <c r="C67">
+        <v>-13.41592082677089</v>
+      </c>
+      <c r="D67">
+        <v>4.406079173229107</v>
+      </c>
+      <c r="E67">
+        <v>3.865</v>
+      </c>
+      <c r="F67">
+        <v>18.265</v>
+      </c>
+      <c r="G67">
+        <v>0.443</v>
+      </c>
+      <c r="H67">
+        <v>13.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.44</v>
+      </c>
+      <c r="K67">
+        <v>0.334</v>
+      </c>
+      <c r="L67">
+        <v>0.106</v>
+      </c>
+      <c r="M67">
+        <v>4.361682</v>
+      </c>
+      <c r="N67">
+        <v>-4.255682</v>
+      </c>
+      <c r="O67">
+        <v>-1.19159096</v>
+      </c>
+      <c r="P67">
+        <v>-3.06409104</v>
+      </c>
+      <c r="Q67">
+        <v>-2.73009104</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1208545719032049</v>
+      </c>
+      <c r="T67">
+        <v>1.387406794269539</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.006804714328096362</v>
+      </c>
+      <c r="W67">
+        <v>0.2371750342184506</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.02430255117177271</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1984628724081146</v>
+      </c>
+      <c r="C68">
+        <v>-13.75211310919416</v>
+      </c>
+      <c r="D68">
+        <v>4.350886890805849</v>
+      </c>
+      <c r="E68">
+        <v>4.146000000000003</v>
+      </c>
+      <c r="F68">
+        <v>18.546</v>
+      </c>
+      <c r="G68">
+        <v>0.443</v>
+      </c>
+      <c r="H68">
+        <v>13.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.44</v>
+      </c>
+      <c r="K68">
+        <v>0.334</v>
+      </c>
+      <c r="L68">
+        <v>0.106</v>
+      </c>
+      <c r="M68">
+        <v>4.428784800000001</v>
+      </c>
+      <c r="N68">
+        <v>-4.322784800000001</v>
+      </c>
+      <c r="O68">
+        <v>-1.210379744</v>
+      </c>
+      <c r="P68">
+        <v>-3.112405056000001</v>
+      </c>
+      <c r="Q68">
+        <v>-2.778405056</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1232679416650638</v>
+      </c>
+      <c r="T68">
+        <v>1.428212876453937</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.006701612595852477</v>
+      </c>
+      <c r="W68">
+        <v>0.2371996549121105</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.02393433069947315</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2004628724081146</v>
+      </c>
+      <c r="C69">
+        <v>-14.08693977732142</v>
+      </c>
+      <c r="D69">
+        <v>4.297060222678579</v>
+      </c>
+      <c r="E69">
+        <v>4.427000000000001</v>
+      </c>
+      <c r="F69">
+        <v>18.827</v>
+      </c>
+      <c r="G69">
+        <v>0.443</v>
+      </c>
+      <c r="H69">
+        <v>13.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.44</v>
+      </c>
+      <c r="K69">
+        <v>0.334</v>
+      </c>
+      <c r="L69">
+        <v>0.106</v>
+      </c>
+      <c r="M69">
+        <v>4.495887600000001</v>
+      </c>
+      <c r="N69">
+        <v>-4.389887600000001</v>
+      </c>
+      <c r="O69">
+        <v>-1.229168528</v>
+      </c>
+      <c r="P69">
+        <v>-3.160719072</v>
+      </c>
+      <c r="Q69">
+        <v>-2.826719072</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1258275762609748</v>
+      </c>
+      <c r="T69">
+        <v>1.471492054528299</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.006601588527257664</v>
+      </c>
+      <c r="W69">
+        <v>0.2372235406596909</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.02357710188306306</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2024628724081146</v>
+      </c>
+      <c r="C70">
+        <v>-14.42045089556653</v>
+      </c>
+      <c r="D70">
+        <v>4.244549104433474</v>
+      </c>
+      <c r="E70">
+        <v>4.708000000000004</v>
+      </c>
+      <c r="F70">
+        <v>19.108</v>
+      </c>
+      <c r="G70">
+        <v>0.443</v>
+      </c>
+      <c r="H70">
+        <v>13.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.44</v>
+      </c>
+      <c r="K70">
+        <v>0.334</v>
+      </c>
+      <c r="L70">
+        <v>0.106</v>
+      </c>
+      <c r="M70">
+        <v>4.562990400000001</v>
+      </c>
+      <c r="N70">
+        <v>-4.456990400000001</v>
+      </c>
+      <c r="O70">
+        <v>-1.247957312</v>
+      </c>
+      <c r="P70">
+        <v>-3.209033088000001</v>
+      </c>
+      <c r="Q70">
+        <v>-2.875033088000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1285471880191303</v>
+      </c>
+      <c r="T70">
+        <v>1.517476181232309</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.006504506343033286</v>
+      </c>
+      <c r="W70">
+        <v>0.2372467238852837</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.02323037979654741</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2044628724081146</v>
+      </c>
+      <c r="C71">
+        <v>-14.75269411069052</v>
+      </c>
+      <c r="D71">
+        <v>4.19330588930948</v>
+      </c>
+      <c r="E71">
+        <v>4.989000000000003</v>
+      </c>
+      <c r="F71">
+        <v>19.389</v>
+      </c>
+      <c r="G71">
+        <v>0.443</v>
+      </c>
+      <c r="H71">
+        <v>13.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.44</v>
+      </c>
+      <c r="K71">
+        <v>0.334</v>
+      </c>
+      <c r="L71">
+        <v>0.106</v>
+      </c>
+      <c r="M71">
+        <v>4.630093200000001</v>
+      </c>
+      <c r="N71">
+        <v>-4.524093200000001</v>
+      </c>
+      <c r="O71">
+        <v>-1.266746096000001</v>
+      </c>
+      <c r="P71">
+        <v>-3.257347104000001</v>
+      </c>
+      <c r="Q71">
+        <v>-2.923347104000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1314422586003926</v>
+      </c>
+      <c r="T71">
+        <v>1.56642702578819</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.006410238135163238</v>
+      </c>
+      <c r="W71">
+        <v>0.237269235133323</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.02289370762558296</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2064628724081146</v>
+      </c>
+      <c r="C72">
+        <v>-15.08371479599886</v>
+      </c>
+      <c r="D72">
+        <v>4.143285204001141</v>
+      </c>
+      <c r="E72">
+        <v>5.270000000000001</v>
+      </c>
+      <c r="F72">
+        <v>19.67</v>
+      </c>
+      <c r="G72">
+        <v>0.443</v>
+      </c>
+      <c r="H72">
+        <v>13.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.44</v>
+      </c>
+      <c r="K72">
+        <v>0.334</v>
+      </c>
+      <c r="L72">
+        <v>0.106</v>
+      </c>
+      <c r="M72">
+        <v>4.697196000000001</v>
+      </c>
+      <c r="N72">
+        <v>-4.591196000000001</v>
+      </c>
+      <c r="O72">
+        <v>-1.28553488</v>
+      </c>
+      <c r="P72">
+        <v>-3.305661120000001</v>
+      </c>
+      <c r="Q72">
+        <v>-2.971661120000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1345303338870723</v>
+      </c>
+      <c r="T72">
+        <v>1.618641259981129</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.006318663304660906</v>
+      </c>
+      <c r="W72">
+        <v>0.237291103202847</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.02256665465950325</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2084628724081146</v>
+      </c>
+      <c r="C73">
+        <v>-15.41355618533989</v>
+      </c>
+      <c r="D73">
+        <v>4.094443814660112</v>
+      </c>
+      <c r="E73">
+        <v>5.551</v>
+      </c>
+      <c r="F73">
+        <v>19.951</v>
+      </c>
+      <c r="G73">
+        <v>0.443</v>
+      </c>
+      <c r="H73">
+        <v>13.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.44</v>
+      </c>
+      <c r="K73">
+        <v>0.334</v>
+      </c>
+      <c r="L73">
+        <v>0.106</v>
+      </c>
+      <c r="M73">
+        <v>4.764298800000001</v>
+      </c>
+      <c r="N73">
+        <v>-4.658298800000001</v>
+      </c>
+      <c r="O73">
+        <v>-1.304323664</v>
+      </c>
+      <c r="P73">
+        <v>-3.353975136</v>
+      </c>
+      <c r="Q73">
+        <v>-3.019975136</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1378313798831783</v>
+      </c>
+      <c r="T73">
+        <v>1.674456475842547</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.006229668046848782</v>
+      </c>
+      <c r="W73">
+        <v>0.2373123552704125</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.02224881445303128</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2104628724081146</v>
+      </c>
+      <c r="C74">
+        <v>-15.74225949773613</v>
+      </c>
+      <c r="D74">
+        <v>4.046740502263869</v>
+      </c>
+      <c r="E74">
+        <v>5.831999999999999</v>
+      </c>
+      <c r="F74">
+        <v>20.232</v>
+      </c>
+      <c r="G74">
+        <v>0.443</v>
+      </c>
+      <c r="H74">
+        <v>13.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.44</v>
+      </c>
+      <c r="K74">
+        <v>0.334</v>
+      </c>
+      <c r="L74">
+        <v>0.106</v>
+      </c>
+      <c r="M74">
+        <v>4.8314016</v>
+      </c>
+      <c r="N74">
+        <v>-4.725401600000001</v>
+      </c>
+      <c r="O74">
+        <v>-1.323112448</v>
+      </c>
+      <c r="P74">
+        <v>-3.402289152</v>
+      </c>
+      <c r="Q74">
+        <v>-3.068289152</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.141368214879006</v>
+      </c>
+      <c r="T74">
+        <v>1.734258492836924</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.006143144879531438</v>
+      </c>
+      <c r="W74">
+        <v>0.2373330170027679</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.02193980314118371</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2124628724081146</v>
+      </c>
+      <c r="C75">
+        <v>-16.06986405340367</v>
+      </c>
+      <c r="D75">
+        <v>4.000135946596333</v>
+      </c>
+      <c r="E75">
+        <v>6.113000000000001</v>
+      </c>
+      <c r="F75">
+        <v>20.513</v>
+      </c>
+      <c r="G75">
+        <v>0.443</v>
+      </c>
+      <c r="H75">
+        <v>13.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.44</v>
+      </c>
+      <c r="K75">
+        <v>0.334</v>
+      </c>
+      <c r="L75">
+        <v>0.106</v>
+      </c>
+      <c r="M75">
+        <v>4.898504400000001</v>
+      </c>
+      <c r="N75">
+        <v>-4.792504400000001</v>
+      </c>
+      <c r="O75">
+        <v>-1.341901232000001</v>
+      </c>
+      <c r="P75">
+        <v>-3.450603168000001</v>
+      </c>
+      <c r="Q75">
+        <v>-3.116603168000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1451670376523025</v>
+      </c>
+      <c r="T75">
+        <v>1.798490288867921</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.006058992209948814</v>
+      </c>
+      <c r="W75">
+        <v>0.2373531126602642</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.02163925789267429</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2144628724081146</v>
+      </c>
+      <c r="C76">
+        <v>-16.39640738184592</v>
+      </c>
+      <c r="D76">
+        <v>3.954592618154078</v>
+      </c>
+      <c r="E76">
+        <v>6.394</v>
+      </c>
+      <c r="F76">
+        <v>20.794</v>
+      </c>
+      <c r="G76">
+        <v>0.443</v>
+      </c>
+      <c r="H76">
+        <v>13.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.44</v>
+      </c>
+      <c r="K76">
+        <v>0.334</v>
+      </c>
+      <c r="L76">
+        <v>0.106</v>
+      </c>
+      <c r="M76">
+        <v>4.9656072</v>
+      </c>
+      <c r="N76">
+        <v>-4.8596072</v>
+      </c>
+      <c r="O76">
+        <v>-1.360690016</v>
+      </c>
+      <c r="P76">
+        <v>-3.498917184</v>
+      </c>
+      <c r="Q76">
+        <v>-3.164917184</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1492580775620065</v>
+      </c>
+      <c r="T76">
+        <v>1.867662992285918</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0059771139368414</v>
+      </c>
+      <c r="W76">
+        <v>0.2373726651918823</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.0213468354887193</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2164628724081146</v>
+      </c>
+      <c r="C77">
+        <v>-16.72192532264641</v>
+      </c>
+      <c r="D77">
+        <v>3.910074677353596</v>
+      </c>
+      <c r="E77">
+        <v>6.675000000000002</v>
+      </c>
+      <c r="F77">
+        <v>21.075</v>
+      </c>
+      <c r="G77">
+        <v>0.443</v>
+      </c>
+      <c r="H77">
+        <v>13.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.44</v>
+      </c>
+      <c r="K77">
+        <v>0.334</v>
+      </c>
+      <c r="L77">
+        <v>0.106</v>
+      </c>
+      <c r="M77">
+        <v>5.032710000000001</v>
+      </c>
+      <c r="N77">
+        <v>-4.926710000000001</v>
+      </c>
+      <c r="O77">
+        <v>-1.3794788</v>
+      </c>
+      <c r="P77">
+        <v>-3.547231200000001</v>
+      </c>
+      <c r="Q77">
+        <v>-3.213231200000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1536764006644868</v>
+      </c>
+      <c r="T77">
+        <v>1.942369511977355</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.00589741908435018</v>
+      </c>
+      <c r="W77">
+        <v>0.2373916963226572</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.02106221101553629</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2184628724081146</v>
+      </c>
+      <c r="C78">
+        <v>-17.04645211952931</v>
+      </c>
+      <c r="D78">
+        <v>3.866547880470696</v>
+      </c>
+      <c r="E78">
+        <v>6.956000000000001</v>
+      </c>
+      <c r="F78">
+        <v>21.356</v>
+      </c>
+      <c r="G78">
+        <v>0.443</v>
+      </c>
+      <c r="H78">
+        <v>13.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.44</v>
+      </c>
+      <c r="K78">
+        <v>0.334</v>
+      </c>
+      <c r="L78">
+        <v>0.106</v>
+      </c>
+      <c r="M78">
+        <v>5.0998128</v>
+      </c>
+      <c r="N78">
+        <v>-4.993812800000001</v>
+      </c>
+      <c r="O78">
+        <v>-1.398267584</v>
+      </c>
+      <c r="P78">
+        <v>-3.595545216000001</v>
+      </c>
+      <c r="Q78">
+        <v>-3.261545216</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1584629173588404</v>
+      </c>
+      <c r="T78">
+        <v>2.023301574976412</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.005819821464819257</v>
+      </c>
+      <c r="W78">
+        <v>0.2374102266342012</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.02078507666006879</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2204628724081146</v>
+      </c>
+      <c r="C79">
+        <v>-17.37002050820682</v>
+      </c>
+      <c r="D79">
+        <v>3.823979491793182</v>
+      </c>
+      <c r="E79">
+        <v>7.237</v>
+      </c>
+      <c r="F79">
+        <v>21.637</v>
+      </c>
+      <c r="G79">
+        <v>0.443</v>
+      </c>
+      <c r="H79">
+        <v>13.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.44</v>
+      </c>
+      <c r="K79">
+        <v>0.334</v>
+      </c>
+      <c r="L79">
+        <v>0.106</v>
+      </c>
+      <c r="M79">
+        <v>5.1669156</v>
+      </c>
+      <c r="N79">
+        <v>-5.0609156</v>
+      </c>
+      <c r="O79">
+        <v>-1.417056368</v>
+      </c>
+      <c r="P79">
+        <v>-3.643859232</v>
+      </c>
+      <c r="Q79">
+        <v>-3.309859232</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1636656528961813</v>
+      </c>
+      <c r="T79">
+        <v>2.111271208671038</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.005744239367873552</v>
+      </c>
+      <c r="W79">
+        <v>0.2374282756389518</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.0205151405995484</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2224628724081146</v>
+      </c>
+      <c r="C80">
+        <v>-17.69266179848672</v>
+      </c>
+      <c r="D80">
+        <v>3.782338201513285</v>
+      </c>
+      <c r="E80">
+        <v>7.518000000000002</v>
+      </c>
+      <c r="F80">
+        <v>21.918</v>
+      </c>
+      <c r="G80">
+        <v>0.443</v>
+      </c>
+      <c r="H80">
+        <v>13.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.44</v>
+      </c>
+      <c r="K80">
+        <v>0.334</v>
+      </c>
+      <c r="L80">
+        <v>0.106</v>
+      </c>
+      <c r="M80">
+        <v>5.234018400000001</v>
+      </c>
+      <c r="N80">
+        <v>-5.128018400000001</v>
+      </c>
+      <c r="O80">
+        <v>-1.435845152</v>
+      </c>
+      <c r="P80">
+        <v>-3.692173248</v>
+      </c>
+      <c r="Q80">
+        <v>-3.358173248</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1693413643914623</v>
+      </c>
+      <c r="T80">
+        <v>2.207238081792449</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.005670595273413634</v>
+      </c>
+      <c r="W80">
+        <v>0.2374458618487088</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.0202521259764773</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2244628724081146</v>
+      </c>
+      <c r="C81">
+        <v>-18.01440595107312</v>
+      </c>
+      <c r="D81">
+        <v>3.741594048926879</v>
+      </c>
+      <c r="E81">
+        <v>7.799000000000001</v>
+      </c>
+      <c r="F81">
+        <v>22.199</v>
+      </c>
+      <c r="G81">
+        <v>0.443</v>
+      </c>
+      <c r="H81">
+        <v>13.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.44</v>
+      </c>
+      <c r="K81">
+        <v>0.334</v>
+      </c>
+      <c r="L81">
+        <v>0.106</v>
+      </c>
+      <c r="M81">
+        <v>5.301121200000001</v>
+      </c>
+      <c r="N81">
+        <v>-5.195121200000001</v>
+      </c>
+      <c r="O81">
+        <v>-1.454633936</v>
+      </c>
+      <c r="P81">
+        <v>-3.740487264</v>
+      </c>
+      <c r="Q81">
+        <v>-3.406487264</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.1755576198386747</v>
+      </c>
+      <c r="T81">
+        <v>2.312344657115899</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.005598815586408398</v>
+      </c>
+      <c r="W81">
+        <v>0.2374630028379657</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.01999576995145858</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2264628724081146</v>
+      </c>
+      <c r="C82">
+        <v>-18.33528164945623</v>
+      </c>
+      <c r="D82">
+        <v>3.701718350543774</v>
+      </c>
+      <c r="E82">
+        <v>8.080000000000004</v>
+      </c>
+      <c r="F82">
+        <v>22.48</v>
+      </c>
+      <c r="G82">
+        <v>0.443</v>
+      </c>
+      <c r="H82">
+        <v>13.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.44</v>
+      </c>
+      <c r="K82">
+        <v>0.334</v>
+      </c>
+      <c r="L82">
+        <v>0.106</v>
+      </c>
+      <c r="M82">
+        <v>5.368224000000001</v>
+      </c>
+      <c r="N82">
+        <v>-5.262224000000002</v>
+      </c>
+      <c r="O82">
+        <v>-1.473422720000001</v>
+      </c>
+      <c r="P82">
+        <v>-3.788801280000001</v>
+      </c>
+      <c r="Q82">
+        <v>-3.454801280000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.1823955008306085</v>
+      </c>
+      <c r="T82">
+        <v>2.427961889971694</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.005528830391578293</v>
+      </c>
+      <c r="W82">
+        <v>0.2374797153024911</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.01974582282706527</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2284628724081146</v>
+      </c>
+      <c r="C83">
+        <v>-18.65531636725359</v>
+      </c>
+      <c r="D83">
+        <v>3.66268363274641</v>
+      </c>
+      <c r="E83">
+        <v>8.361000000000002</v>
+      </c>
+      <c r="F83">
+        <v>22.761</v>
+      </c>
+      <c r="G83">
+        <v>0.443</v>
+      </c>
+      <c r="H83">
+        <v>13.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.44</v>
+      </c>
+      <c r="K83">
+        <v>0.334</v>
+      </c>
+      <c r="L83">
+        <v>0.106</v>
+      </c>
+      <c r="M83">
+        <v>5.435326800000001</v>
+      </c>
+      <c r="N83">
+        <v>-5.329326800000001</v>
+      </c>
+      <c r="O83">
+        <v>-1.492211504000001</v>
+      </c>
+      <c r="P83">
+        <v>-3.837115296000001</v>
+      </c>
+      <c r="Q83">
+        <v>-3.503115296000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.1899531587690616</v>
+      </c>
+      <c r="T83">
+        <v>2.555749357864941</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.005460573226250166</v>
+      </c>
+      <c r="W83">
+        <v>0.2374960151135715</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.01950204723660776</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2304628724081146</v>
+      </c>
+      <c r="C84">
+        <v>-18.97453643133514</v>
+      </c>
+      <c r="D84">
+        <v>3.624463568664859</v>
+      </c>
+      <c r="E84">
+        <v>8.642000000000001</v>
+      </c>
+      <c r="F84">
+        <v>23.042</v>
+      </c>
+      <c r="G84">
+        <v>0.443</v>
+      </c>
+      <c r="H84">
+        <v>13.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.44</v>
+      </c>
+      <c r="K84">
+        <v>0.334</v>
+      </c>
+      <c r="L84">
+        <v>0.106</v>
+      </c>
+      <c r="M84">
+        <v>5.502429600000001</v>
+      </c>
+      <c r="N84">
+        <v>-5.396429600000001</v>
+      </c>
+      <c r="O84">
+        <v>-1.511000288</v>
+      </c>
+      <c r="P84">
+        <v>-3.885429312000001</v>
+      </c>
+      <c r="Q84">
+        <v>-3.551429312000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.1983505564784539</v>
+      </c>
+      <c r="T84">
+        <v>2.697735433301882</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.005393980869832482</v>
+      </c>
+      <c r="W84">
+        <v>0.237511917368284</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.01926421739225881</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2324628724081146</v>
+      </c>
+      <c r="C85">
+        <v>-19.29296708103683</v>
+      </c>
+      <c r="D85">
+        <v>3.587032918963177</v>
+      </c>
+      <c r="E85">
+        <v>8.923000000000004</v>
+      </c>
+      <c r="F85">
+        <v>23.323</v>
+      </c>
+      <c r="G85">
+        <v>0.443</v>
+      </c>
+      <c r="H85">
+        <v>13.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.44</v>
+      </c>
+      <c r="K85">
+        <v>0.334</v>
+      </c>
+      <c r="L85">
+        <v>0.106</v>
+      </c>
+      <c r="M85">
+        <v>5.569532400000001</v>
+      </c>
+      <c r="N85">
+        <v>-5.463532400000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.529789072</v>
+      </c>
+      <c r="P85">
+        <v>-3.933743328</v>
+      </c>
+      <c r="Q85">
+        <v>-3.599743328</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2077358833301277</v>
+      </c>
+      <c r="T85">
+        <v>2.856425752907876</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.005328993148509199</v>
+      </c>
+      <c r="W85">
+        <v>0.237527436436136</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.01903211838753283</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2344628724081146</v>
+      </c>
+      <c r="C86">
+        <v>-19.6106325237426</v>
+      </c>
+      <c r="D86">
+        <v>3.550367476257401</v>
+      </c>
+      <c r="E86">
+        <v>9.203999999999999</v>
+      </c>
+      <c r="F86">
+        <v>23.604</v>
+      </c>
+      <c r="G86">
+        <v>0.443</v>
+      </c>
+      <c r="H86">
+        <v>13.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.44</v>
+      </c>
+      <c r="K86">
+        <v>0.334</v>
+      </c>
+      <c r="L86">
+        <v>0.106</v>
+      </c>
+      <c r="M86">
+        <v>5.6366352</v>
+      </c>
+      <c r="N86">
+        <v>-5.5306352</v>
+      </c>
+      <c r="O86">
+        <v>-1.548577856</v>
+      </c>
+      <c r="P86">
+        <v>-3.982057344</v>
+      </c>
+      <c r="Q86">
+        <v>-3.648057344</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2182943760382606</v>
+      </c>
+      <c r="T86">
+        <v>3.034952362464617</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.00526555275388409</v>
+      </c>
+      <c r="W86">
+        <v>0.2375425860023725</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.01880554554958602</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2364628724081146</v>
+      </c>
+      <c r="C87">
+        <v>-19.92755598709212</v>
+      </c>
+      <c r="D87">
+        <v>3.514444012907877</v>
+      </c>
+      <c r="E87">
+        <v>9.485000000000001</v>
+      </c>
+      <c r="F87">
+        <v>23.885</v>
+      </c>
+      <c r="G87">
+        <v>0.443</v>
+      </c>
+      <c r="H87">
+        <v>13.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.44</v>
+      </c>
+      <c r="K87">
+        <v>0.334</v>
+      </c>
+      <c r="L87">
+        <v>0.106</v>
+      </c>
+      <c r="M87">
+        <v>5.703738</v>
+      </c>
+      <c r="N87">
+        <v>-5.597738000000001</v>
+      </c>
+      <c r="O87">
+        <v>-1.56736664</v>
+      </c>
+      <c r="P87">
+        <v>-4.03037136</v>
+      </c>
+      <c r="Q87">
+        <v>-3.69637136</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2302606677741446</v>
+      </c>
+      <c r="T87">
+        <v>3.237282519962258</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.00520360507442663</v>
+      </c>
+      <c r="W87">
+        <v>0.2375573791082269</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.01858430383723797</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2384628724081146</v>
+      </c>
+      <c r="C88">
+        <v>-20.2437597680507</v>
+      </c>
+      <c r="D88">
+        <v>3.479240231949302</v>
+      </c>
+      <c r="E88">
+        <v>9.766</v>
+      </c>
+      <c r="F88">
+        <v>24.166</v>
+      </c>
+      <c r="G88">
+        <v>0.443</v>
+      </c>
+      <c r="H88">
+        <v>13.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.44</v>
+      </c>
+      <c r="K88">
+        <v>0.334</v>
+      </c>
+      <c r="L88">
+        <v>0.106</v>
+      </c>
+      <c r="M88">
+        <v>5.7708408</v>
+      </c>
+      <c r="N88">
+        <v>-5.6648408</v>
+      </c>
+      <c r="O88">
+        <v>-1.586155424</v>
+      </c>
+      <c r="P88">
+        <v>-4.078685376</v>
+      </c>
+      <c r="Q88">
+        <v>-3.744685376</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2439364297580121</v>
+      </c>
+      <c r="T88">
+        <v>3.468516985673848</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.005143098038677483</v>
+      </c>
+      <c r="W88">
+        <v>0.2375718281883638</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.01836820728099098</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2404628724081146</v>
+      </c>
+      <c r="C89">
+        <v>-20.55926527905928</v>
+      </c>
+      <c r="D89">
+        <v>3.444734720940726</v>
+      </c>
+      <c r="E89">
+        <v>10.047</v>
+      </c>
+      <c r="F89">
+        <v>24.447</v>
+      </c>
+      <c r="G89">
+        <v>0.443</v>
+      </c>
+      <c r="H89">
+        <v>13.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.44</v>
+      </c>
+      <c r="K89">
+        <v>0.334</v>
+      </c>
+      <c r="L89">
+        <v>0.106</v>
+      </c>
+      <c r="M89">
+        <v>5.837943600000001</v>
+      </c>
+      <c r="N89">
+        <v>-5.731943600000001</v>
+      </c>
+      <c r="O89">
+        <v>-1.604944208</v>
+      </c>
+      <c r="P89">
+        <v>-4.126999392</v>
+      </c>
+      <c r="Q89">
+        <v>-3.792999392</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.259716155124013</v>
+      </c>
+      <c r="T89">
+        <v>3.735325984571836</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.005083981969267397</v>
+      </c>
+      <c r="W89">
+        <v>0.237585945105739</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.01815707846166925</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2424628724081146</v>
+      </c>
+      <c r="C90">
+        <v>-20.87409309146524</v>
+      </c>
+      <c r="D90">
+        <v>3.410906908534761</v>
+      </c>
+      <c r="E90">
+        <v>10.328</v>
+      </c>
+      <c r="F90">
+        <v>24.728</v>
+      </c>
+      <c r="G90">
+        <v>0.443</v>
+      </c>
+      <c r="H90">
+        <v>13.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.44</v>
+      </c>
+      <c r="K90">
+        <v>0.334</v>
+      </c>
+      <c r="L90">
+        <v>0.106</v>
+      </c>
+      <c r="M90">
+        <v>5.905046400000001</v>
+      </c>
+      <c r="N90">
+        <v>-5.799046400000001</v>
+      </c>
+      <c r="O90">
+        <v>-1.623732992</v>
+      </c>
+      <c r="P90">
+        <v>-4.175313408000001</v>
+      </c>
+      <c r="Q90">
+        <v>-3.841313408000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.2781258347176808</v>
+      </c>
+      <c r="T90">
+        <v>4.046603149952824</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.005026209446889358</v>
+      </c>
+      <c r="W90">
+        <v>0.2375997411840828</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.01795074802460483</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2444628724081146</v>
+      </c>
+      <c r="C91">
+        <v>-21.18826297641916</v>
+      </c>
+      <c r="D91">
+        <v>3.377737023580843</v>
+      </c>
+      <c r="E91">
+        <v>10.609</v>
+      </c>
+      <c r="F91">
+        <v>25.009</v>
+      </c>
+      <c r="G91">
+        <v>0.443</v>
+      </c>
+      <c r="H91">
+        <v>13.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.44</v>
+      </c>
+      <c r="K91">
+        <v>0.334</v>
+      </c>
+      <c r="L91">
+        <v>0.106</v>
+      </c>
+      <c r="M91">
+        <v>5.9721492</v>
+      </c>
+      <c r="N91">
+        <v>-5.866149200000001</v>
+      </c>
+      <c r="O91">
+        <v>-1.642521776</v>
+      </c>
+      <c r="P91">
+        <v>-4.223627424</v>
+      </c>
+      <c r="Q91">
+        <v>-3.889627424</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.2998827287829245</v>
+      </c>
+      <c r="T91">
+        <v>4.414476163584898</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.004969735183441164</v>
+      </c>
+      <c r="W91">
+        <v>0.2376132272381943</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.01774905422657558</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2464628724081146</v>
+      </c>
+      <c r="C92">
+        <v>-21.50179394340822</v>
+      </c>
+      <c r="D92">
+        <v>3.345206056591785</v>
+      </c>
+      <c r="E92">
+        <v>10.89</v>
+      </c>
+      <c r="F92">
+        <v>25.29</v>
+      </c>
+      <c r="G92">
+        <v>0.443</v>
+      </c>
+      <c r="H92">
+        <v>13.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.44</v>
+      </c>
+      <c r="K92">
+        <v>0.334</v>
+      </c>
+      <c r="L92">
+        <v>0.106</v>
+      </c>
+      <c r="M92">
+        <v>6.039252000000001</v>
+      </c>
+      <c r="N92">
+        <v>-5.933252000000001</v>
+      </c>
+      <c r="O92">
+        <v>-1.66131056</v>
+      </c>
+      <c r="P92">
+        <v>-4.271941440000001</v>
+      </c>
+      <c r="Q92">
+        <v>-3.937941440000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.325991001661217</v>
+      </c>
+      <c r="T92">
+        <v>4.855923779943388</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.004914515903625149</v>
+      </c>
+      <c r="W92">
+        <v>0.2376264136022143</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.01755184251294695</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2484628724081146</v>
+      </c>
+      <c r="C93">
+        <v>-21.81470427658423</v>
+      </c>
+      <c r="D93">
+        <v>3.313295723415767</v>
+      </c>
+      <c r="E93">
+        <v>11.171</v>
+      </c>
+      <c r="F93">
+        <v>25.571</v>
+      </c>
+      <c r="G93">
+        <v>0.443</v>
+      </c>
+      <c r="H93">
+        <v>13.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.44</v>
+      </c>
+      <c r="K93">
+        <v>0.334</v>
+      </c>
+      <c r="L93">
+        <v>0.106</v>
+      </c>
+      <c r="M93">
+        <v>6.106354800000001</v>
+      </c>
+      <c r="N93">
+        <v>-6.000354800000001</v>
+      </c>
+      <c r="O93">
+        <v>-1.680099344</v>
+      </c>
+      <c r="P93">
+        <v>-4.320255456000001</v>
+      </c>
+      <c r="Q93">
+        <v>-3.986255456000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.3579011129569077</v>
+      </c>
+      <c r="T93">
+        <v>5.395470866603764</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.004860510234354545</v>
+      </c>
+      <c r="W93">
+        <v>0.2376393101560361</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.01735896512269475</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2504628724081146</v>
+      </c>
+      <c r="C94">
+        <v>-22.12701156903208</v>
+      </c>
+      <c r="D94">
+        <v>3.281988430967924</v>
+      </c>
+      <c r="E94">
+        <v>11.452</v>
+      </c>
+      <c r="F94">
+        <v>25.852</v>
+      </c>
+      <c r="G94">
+        <v>0.443</v>
+      </c>
+      <c r="H94">
+        <v>13.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.44</v>
+      </c>
+      <c r="K94">
+        <v>0.334</v>
+      </c>
+      <c r="L94">
+        <v>0.106</v>
+      </c>
+      <c r="M94">
+        <v>6.173457600000002</v>
+      </c>
+      <c r="N94">
+        <v>-6.067457600000002</v>
+      </c>
+      <c r="O94">
+        <v>-1.698888128000001</v>
+      </c>
+      <c r="P94">
+        <v>-4.368569472000001</v>
+      </c>
+      <c r="Q94">
+        <v>-4.034569472000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.3977887520765214</v>
+      </c>
+      <c r="T94">
+        <v>6.069904724929238</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.004807678601372429</v>
+      </c>
+      <c r="W94">
+        <v>0.2376519263499923</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.01717028071918725</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2524628724081146</v>
+      </c>
+      <c r="C95">
+        <v>-22.43873275511348</v>
+      </c>
+      <c r="D95">
+        <v>3.251267244886526</v>
+      </c>
+      <c r="E95">
+        <v>11.733</v>
+      </c>
+      <c r="F95">
+        <v>26.133</v>
+      </c>
+      <c r="G95">
+        <v>0.443</v>
+      </c>
+      <c r="H95">
+        <v>13.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.44</v>
+      </c>
+      <c r="K95">
+        <v>0.334</v>
+      </c>
+      <c r="L95">
+        <v>0.106</v>
+      </c>
+      <c r="M95">
+        <v>6.240560400000001</v>
+      </c>
+      <c r="N95">
+        <v>-6.134560400000001</v>
+      </c>
+      <c r="O95">
+        <v>-1.717676912</v>
+      </c>
+      <c r="P95">
+        <v>-4.416883488</v>
+      </c>
+      <c r="Q95">
+        <v>-4.082883488</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.4490728595160244</v>
+      </c>
+      <c r="T95">
+        <v>6.937033971347701</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.004755983132540468</v>
+      </c>
+      <c r="W95">
+        <v>0.2376642712279494</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.01698565404478736</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2544628724081146</v>
+      </c>
+      <c r="C96">
+        <v>-22.74988414101113</v>
+      </c>
+      <c r="D96">
+        <v>3.221115858988873</v>
+      </c>
+      <c r="E96">
+        <v>12.014</v>
+      </c>
+      <c r="F96">
+        <v>26.414</v>
+      </c>
+      <c r="G96">
+        <v>0.443</v>
+      </c>
+      <c r="H96">
+        <v>13.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.44</v>
+      </c>
+      <c r="K96">
+        <v>0.334</v>
+      </c>
+      <c r="L96">
+        <v>0.106</v>
+      </c>
+      <c r="M96">
+        <v>6.3076632</v>
+      </c>
+      <c r="N96">
+        <v>-6.2016632</v>
+      </c>
+      <c r="O96">
+        <v>-1.736465696</v>
+      </c>
+      <c r="P96">
+        <v>-4.465197504000001</v>
+      </c>
+      <c r="Q96">
+        <v>-4.131197504000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.5174516694353621</v>
+      </c>
+      <c r="T96">
+        <v>8.093206299905654</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.004705387567300676</v>
+      </c>
+      <c r="W96">
+        <v>0.2376763534489286</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.01680495559750239</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2564628724081146</v>
+      </c>
+      <c r="C97">
+        <v>-23.06048143358889</v>
+      </c>
+      <c r="D97">
+        <v>3.191518566411116</v>
+      </c>
+      <c r="E97">
+        <v>12.295</v>
+      </c>
+      <c r="F97">
+        <v>26.695</v>
+      </c>
+      <c r="G97">
+        <v>0.443</v>
+      </c>
+      <c r="H97">
+        <v>13.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.44</v>
+      </c>
+      <c r="K97">
+        <v>0.334</v>
+      </c>
+      <c r="L97">
+        <v>0.106</v>
+      </c>
+      <c r="M97">
+        <v>6.374766000000001</v>
+      </c>
+      <c r="N97">
+        <v>-6.268766000000001</v>
+      </c>
+      <c r="O97">
+        <v>-1.755254480000001</v>
+      </c>
+      <c r="P97">
+        <v>-4.513511520000001</v>
+      </c>
+      <c r="Q97">
+        <v>-4.179511520000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.6131820033224347</v>
+      </c>
+      <c r="T97">
+        <v>9.711847559886788</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.004655857171855405</v>
+      </c>
+      <c r="W97">
+        <v>0.2376881813073609</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.01662806132805494</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2584628724081146</v>
+      </c>
+      <c r="C98">
+        <v>-23.37053976767532</v>
+      </c>
+      <c r="D98">
+        <v>3.162460232324677</v>
+      </c>
+      <c r="E98">
+        <v>12.576</v>
+      </c>
+      <c r="F98">
+        <v>26.976</v>
+      </c>
+      <c r="G98">
+        <v>0.443</v>
+      </c>
+      <c r="H98">
+        <v>13.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.44</v>
+      </c>
+      <c r="K98">
+        <v>0.334</v>
+      </c>
+      <c r="L98">
+        <v>0.106</v>
+      </c>
+      <c r="M98">
+        <v>6.4418688</v>
+      </c>
+      <c r="N98">
+        <v>-6.3358688</v>
+      </c>
+      <c r="O98">
+        <v>-1.774043264</v>
+      </c>
+      <c r="P98">
+        <v>-4.561825536</v>
+      </c>
+      <c r="Q98">
+        <v>-4.227825536</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.7567775041530418</v>
+      </c>
+      <c r="T98">
+        <v>12.13980944985846</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.004607358659648579</v>
+      </c>
+      <c r="W98">
+        <v>0.2376997627520759</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.01645485235588773</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2604628724081146</v>
+      </c>
+      <c r="C99">
+        <v>-23.6800737318703</v>
+      </c>
+      <c r="D99">
+        <v>3.133926268129698</v>
+      </c>
+      <c r="E99">
+        <v>12.857</v>
+      </c>
+      <c r="F99">
+        <v>27.257</v>
+      </c>
+      <c r="G99">
+        <v>0.443</v>
+      </c>
+      <c r="H99">
+        <v>13.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.44</v>
+      </c>
+      <c r="K99">
+        <v>0.334</v>
+      </c>
+      <c r="L99">
+        <v>0.106</v>
+      </c>
+      <c r="M99">
+        <v>6.508971600000001</v>
+      </c>
+      <c r="N99">
+        <v>-6.402971600000001</v>
+      </c>
+      <c r="O99">
+        <v>-1.792832048</v>
+      </c>
+      <c r="P99">
+        <v>-4.610139552000001</v>
+      </c>
+      <c r="Q99">
+        <v>-4.276139552000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>0.9961033388707226</v>
+      </c>
+      <c r="T99">
+        <v>16.18641259981128</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.004559860116765604</v>
+      </c>
+      <c r="W99">
+        <v>0.2377111054041164</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.01628521470273425</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2624628724081146</v>
+      </c>
+      <c r="C100">
+        <v>-23.98909739296692</v>
+      </c>
+      <c r="D100">
+        <v>3.105902607033086</v>
+      </c>
+      <c r="E100">
+        <v>13.138</v>
+      </c>
+      <c r="F100">
+        <v>27.538</v>
+      </c>
+      <c r="G100">
+        <v>0.443</v>
+      </c>
+      <c r="H100">
+        <v>13.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.44</v>
+      </c>
+      <c r="K100">
+        <v>0.334</v>
+      </c>
+      <c r="L100">
+        <v>0.106</v>
+      </c>
+      <c r="M100">
+        <v>6.5760744</v>
+      </c>
+      <c r="N100">
+        <v>-6.470074400000001</v>
+      </c>
+      <c r="O100">
+        <v>-1.811620832</v>
+      </c>
+      <c r="P100">
+        <v>-4.658453568000001</v>
+      </c>
+      <c r="Q100">
+        <v>-4.324453568000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.474755008306083</v>
+      </c>
+      <c r="T100">
+        <v>24.27961889971692</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.004513330931900648</v>
+      </c>
+      <c r="W100">
+        <v>0.2377222165734621</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.01611903904250234</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2644628724081146</v>
+      </c>
+      <c r="C101">
+        <v>-24.29762431907478</v>
+      </c>
+      <c r="D101">
+        <v>3.078375680925224</v>
+      </c>
+      <c r="E101">
+        <v>13.419</v>
+      </c>
+      <c r="F101">
+        <v>27.819</v>
+      </c>
+      <c r="G101">
+        <v>0.443</v>
+      </c>
+      <c r="H101">
+        <v>13.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.44</v>
+      </c>
+      <c r="K101">
+        <v>0.334</v>
+      </c>
+      <c r="L101">
+        <v>0.106</v>
+      </c>
+      <c r="M101">
+        <v>6.643177200000001</v>
+      </c>
+      <c r="N101">
+        <v>-6.537177200000001</v>
+      </c>
+      <c r="O101">
+        <v>-1.830409616000001</v>
+      </c>
+      <c r="P101">
+        <v>-4.706767584000001</v>
+      </c>
+      <c r="Q101">
+        <v>-4.372767584000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>2.910710016612167</v>
+      </c>
+      <c r="T101">
+        <v>48.55923779943383</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.004467741730568318</v>
+      </c>
+      <c r="W101">
+        <v>0.2377331032747403</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.0159562204663154</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
